--- a/text/foundationScores/milkywayoriginal_6_seconds_MFT_MAC.xlsx
+++ b/text/foundationScores/milkywayoriginal_6_seconds_MFT_MAC.xlsx
@@ -425,166 +425,176 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG42"/>
+  <dimension ref="A1:AI42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>chunkEnd</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>chunkStart</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>V_neu</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>V_neg</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>V_pos</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>V_com</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>sentence</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>full_text</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_care_virtue</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_fairness_virtue</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_loyalty_virtue</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_authority_virtue</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_sanctity_virtue</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_care_vice</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_fairness_vice</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_loyalty_vice</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_authority_vice</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_sanctity_vice</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_moral_nonmoral</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_fairness_virtue</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_group_virtue</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_deference_virtue</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_heroism_virtue</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_reciprocity_virtue</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_family_virtue</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_property_virtue</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_fairness_vice</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_group_vice</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_deference_vice</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_heroism_vice</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_reciprocity_vice</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_family_vice</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_property_vice</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_moral_nonmoral</t>
         </is>
@@ -594,104 +604,114 @@
       <c r="A2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>32.997</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>21.142</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
         <v>75.7</v>
       </c>
-      <c r="C2" t="n">
+      <c r="E2" t="n">
         <v>11.9</v>
       </c>
-      <c r="D2" t="n">
+      <c r="F2" t="n">
         <v>12.4</v>
       </c>
-      <c r="E2" t="n">
+      <c r="G2" t="n">
         <v>4.98</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t xml:space="preserve">  He took a deep breath and tried to calm down.  The situation seemed almost hopeless, and after he spent most of the last week's drinking, he knew he must confront the truth.</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>milkywayoriginal_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H2" t="n">
+      <c r="J2" t="n">
         <v>0.007843137254901961</v>
       </c>
-      <c r="I2" t="n">
+      <c r="K2" t="n">
         <v>0.01907968574635241</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>0.02582210800407741</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>0.02976190476190476</v>
       </c>
-      <c r="L2" t="n">
+      <c r="N2" t="n">
         <v>0.04565598243146544</v>
       </c>
-      <c r="M2" t="n">
+      <c r="O2" t="n">
         <v>0.1002128923946837</v>
       </c>
-      <c r="N2" t="n">
+      <c r="P2" t="n">
         <v>0.08785642045549941</v>
       </c>
-      <c r="O2" t="n">
+      <c r="Q2" t="n">
         <v>0.06833840106090745</v>
       </c>
-      <c r="P2" t="n">
+      <c r="R2" t="n">
         <v>0.08558901502429284</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="S2" t="n">
         <v>0.06187276454093173</v>
       </c>
-      <c r="R2" t="n">
+      <c r="T2" t="n">
         <v>2.25</v>
       </c>
-      <c r="S2" t="n">
+      <c r="U2" t="n">
         <v>0.04776115859449193</v>
       </c>
-      <c r="T2" t="n">
+      <c r="V2" t="n">
         <v>0.05032894736842106</v>
       </c>
-      <c r="U2" t="n">
+      <c r="W2" t="n">
         <v>0.03306906378850352</v>
       </c>
-      <c r="V2" t="n">
+      <c r="X2" t="n">
         <v>0.05436954941860465</v>
       </c>
-      <c r="W2" t="n">
+      <c r="Y2" t="n">
         <v>0.08350477056164629</v>
       </c>
-      <c r="X2" t="n">
+      <c r="Z2" t="n">
         <v>0.06837084256439095</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="AA2" t="n">
         <v>0.04942749265055082</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AB2" t="n">
         <v>0.09034708205528189</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AC2" t="n">
         <v>0.1409870312946165</v>
       </c>
-      <c r="AB2" t="n">
+      <c r="AD2" t="n">
         <v>0.1044377319750454</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AE2" t="n">
         <v>0.09162523412782253</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="AF2" t="n">
         <v>0.02887561274509804</v>
       </c>
-      <c r="AE2" t="n">
+      <c r="AG2" t="n">
         <v>0.04838748968268525</v>
       </c>
-      <c r="AF2" t="n">
+      <c r="AH2" t="n">
         <v>0.04168543288351065</v>
       </c>
-      <c r="AG2" t="n">
+      <c r="AI2" t="n">
         <v>1.6</v>
       </c>
     </row>
@@ -699,104 +719,114 @@
       <c r="A3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>46.795</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>34.179</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
         <v>77.8</v>
       </c>
-      <c r="C3" t="n">
+      <c r="E3" t="n">
         <v>22.2</v>
       </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
         <v>-75.06</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t xml:space="preserve">  He looked at his reflection in the mirror and started sobbing uncontrollably.  That evening, at his deepest moment of despair, he did the unthinkable, calling his mother to consult.</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>milkywayoriginal_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H3" t="n">
+      <c r="J3" t="n">
         <v>0.01728395061728395</v>
       </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
         <v>0.04020663689694422</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>0.01149425287356322</v>
       </c>
-      <c r="L3" t="n">
+      <c r="N3" t="n">
         <v>0.01458333333333333</v>
       </c>
-      <c r="M3" t="n">
+      <c r="O3" t="n">
         <v>0.09759255627891253</v>
       </c>
-      <c r="N3" t="n">
+      <c r="P3" t="n">
         <v>0.06042145829831966</v>
       </c>
-      <c r="O3" t="n">
+      <c r="Q3" t="n">
         <v>0.05369175627240143</v>
       </c>
-      <c r="P3" t="n">
+      <c r="R3" t="n">
         <v>0.06888815623412316</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="S3" t="n">
         <v>0.06718427835051546</v>
       </c>
-      <c r="R3" t="n">
+      <c r="T3" t="n">
         <v>0.5555555555555556</v>
       </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
         <v>0.03</v>
       </c>
-      <c r="U3" t="n">
+      <c r="W3" t="n">
         <v>0.03260869565217391</v>
       </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
         <v>0.003731343283582089</v>
       </c>
-      <c r="X3" t="n">
+      <c r="Z3" t="n">
         <v>0.015</v>
       </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
         <v>0.1426882698061501</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AC3" t="n">
         <v>0.114984984984985</v>
       </c>
-      <c r="AB3" t="n">
+      <c r="AD3" t="n">
         <v>0.09702180535513868</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AE3" t="n">
         <v>0.1239916375290411</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AF3" t="n">
         <v>0.1003034458552194</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="AG3" t="n">
         <v>0.1745553395588823</v>
       </c>
-      <c r="AF3" t="n">
+      <c r="AH3" t="n">
         <v>0.1156701440042991</v>
       </c>
-      <c r="AG3" t="n">
+      <c r="AI3" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -804,104 +834,114 @@
       <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>65.155</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>48.057</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
         <v>79.90000000000001</v>
       </c>
-      <c r="C4" t="n">
+      <c r="E4" t="n">
         <v>20.1</v>
       </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
         <v>-86.89</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t xml:space="preserve"> In general, advice from his mother resembled a long and gruesomely painful lecture about all the big mistakes he had made in his life, starting from how he fought to stay in his mother's womb up to the way he had ruined the relationship with Emily L'Amour.</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>milkywayoriginal_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H4" t="n">
+      <c r="J4" t="n">
         <v>0.03280883021805765</v>
       </c>
-      <c r="I4" t="n">
+      <c r="K4" t="n">
         <v>0.02412377497110714</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>0.05132738072529883</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>0.01725046758914501</v>
       </c>
-      <c r="L4" t="n">
+      <c r="N4" t="n">
         <v>0.0414335552485517</v>
       </c>
-      <c r="M4" t="n">
+      <c r="O4" t="n">
         <v>0.0792850190328882</v>
       </c>
-      <c r="N4" t="n">
+      <c r="P4" t="n">
         <v>0.06925032116100535</v>
       </c>
-      <c r="O4" t="n">
+      <c r="Q4" t="n">
         <v>0.03623719019571982</v>
       </c>
-      <c r="P4" t="n">
+      <c r="R4" t="n">
         <v>0.06937078578206049</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="S4" t="n">
         <v>0.0479671776262677</v>
       </c>
-      <c r="R4" t="n">
+      <c r="T4" t="n">
         <v>2</v>
       </c>
-      <c r="S4" t="n">
+      <c r="U4" t="n">
         <v>0.07359536960286261</v>
       </c>
-      <c r="T4" t="n">
+      <c r="V4" t="n">
         <v>0.1181322728103</v>
       </c>
-      <c r="U4" t="n">
+      <c r="W4" t="n">
         <v>0.07857364644703729</v>
       </c>
-      <c r="V4" t="n">
+      <c r="X4" t="n">
         <v>0.08573065501534961</v>
       </c>
-      <c r="W4" t="n">
+      <c r="Y4" t="n">
         <v>0.09341606921444436</v>
       </c>
-      <c r="X4" t="n">
+      <c r="Z4" t="n">
         <v>0.1316177364940198</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="AA4" t="n">
         <v>0.04078423078194715</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AB4" t="n">
         <v>0.1182163165504206</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AC4" t="n">
         <v>0.08020502954663596</v>
       </c>
-      <c r="AB4" t="n">
+      <c r="AD4" t="n">
         <v>0.1078678455727636</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AE4" t="n">
         <v>0.09589857680575596</v>
       </c>
-      <c r="AD4" t="n">
+      <c r="AF4" t="n">
         <v>0.1064204247472838</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AG4" t="n">
         <v>0.1030070823174272</v>
       </c>
-      <c r="AF4" t="n">
+      <c r="AH4" t="n">
         <v>0.0480131049182174</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="AI4" t="n">
         <v>1.1</v>
       </c>
     </row>
@@ -909,104 +949,114 @@
       <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>73.085</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>66.434</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
         <v>66.7</v>
       </c>
-      <c r="C5" t="n">
+      <c r="E5" t="n">
         <v>11.4</v>
       </c>
-      <c r="D5" t="n">
+      <c r="F5" t="n">
         <v>22</v>
       </c>
-      <c r="E5" t="n">
+      <c r="G5" t="n">
         <v>40.19</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t xml:space="preserve">  To be honest, this wasn't far from the truth.  His mother had gone through almost 40 hours of painful labor.</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>milkywayoriginal_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H5" t="n">
+      <c r="J5" t="n">
         <v>0.03017331932773109</v>
       </c>
-      <c r="I5" t="n">
+      <c r="K5" t="n">
         <v>0.06035197311951916</v>
       </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
         <v>0.04692170330994167</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>0.04144693473961767</v>
       </c>
-      <c r="L5" t="n">
+      <c r="N5" t="n">
         <v>0.04116896013618953</v>
       </c>
-      <c r="M5" t="n">
+      <c r="O5" t="n">
         <v>0.07077639760058876</v>
       </c>
-      <c r="N5" t="n">
+      <c r="P5" t="n">
         <v>0.0580643235319362</v>
       </c>
-      <c r="O5" t="n">
+      <c r="Q5" t="n">
         <v>0.04315018315018315</v>
       </c>
-      <c r="P5" t="n">
+      <c r="R5" t="n">
         <v>0.03284599629883767</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="S5" t="n">
         <v>0.03845633533133534</v>
       </c>
-      <c r="R5" t="n">
+      <c r="T5" t="n">
         <v>7</v>
       </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
         <v>0.0958100558659218</v>
       </c>
-      <c r="U5" t="n">
+      <c r="W5" t="n">
         <v>0.04462279293739968</v>
       </c>
-      <c r="V5" t="n">
+      <c r="X5" t="n">
         <v>0.06511627906976744</v>
       </c>
-      <c r="W5" t="n">
+      <c r="Y5" t="n">
         <v>0.07538239538239538</v>
       </c>
-      <c r="X5" t="n">
+      <c r="Z5" t="n">
         <v>0.08700066558436978</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="AA5" t="n">
         <v>0.04017857142857143</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AB5" t="n">
         <v>0.1938577464514496</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AC5" t="n">
         <v>0.09335550935550936</v>
       </c>
-      <c r="AB5" t="n">
+      <c r="AD5" t="n">
         <v>0.06275946275946276</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AE5" t="n">
         <v>0.0805997273966379</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AF5" t="n">
         <v>0.05816070721731099</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="AG5" t="n">
         <v>0.103448275862069</v>
       </c>
-      <c r="AF5" t="n">
+      <c r="AH5" t="n">
         <v>0.06063492063492063</v>
       </c>
-      <c r="AG5" t="n">
+      <c r="AI5" t="n">
         <v>1.666666666666667</v>
       </c>
     </row>
@@ -1014,104 +1064,114 @@
       <c r="A6" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>86.787</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>73.526</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
         <v>74.5</v>
       </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
         <v>25.5</v>
       </c>
-      <c r="E6" t="n">
+      <c r="G6" t="n">
         <v>90.01000000000001</v>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t xml:space="preserve">  He could imagine, though he never actually tried, it could have gone better.  But to this day, every time he looked at his mom's belly, he felt that it was the only place that truly felt safe and warm.</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>milkywayoriginal_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H6" t="n">
+      <c r="J6" t="n">
         <v>0.04345863563137517</v>
       </c>
-      <c r="I6" t="n">
+      <c r="K6" t="n">
         <v>0.04731695003582829</v>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
         <v>0.04611731257772671</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
         <v>0.04093128966200905</v>
       </c>
-      <c r="L6" t="n">
+      <c r="N6" t="n">
         <v>0.03827436452436452</v>
       </c>
-      <c r="M6" t="n">
+      <c r="O6" t="n">
         <v>0.06117157887586434</v>
       </c>
-      <c r="N6" t="n">
+      <c r="P6" t="n">
         <v>0.03475573324005216</v>
       </c>
-      <c r="O6" t="n">
+      <c r="Q6" t="n">
         <v>0.0525110799460512</v>
       </c>
-      <c r="P6" t="n">
+      <c r="R6" t="n">
         <v>0.01958901179367374</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="S6" t="n">
         <v>0.05381044353082095</v>
       </c>
-      <c r="R6" t="n">
+      <c r="T6" t="n">
         <v>4.333333333333333</v>
       </c>
-      <c r="S6" t="n">
+      <c r="U6" t="n">
         <v>0.1080671061528059</v>
       </c>
-      <c r="T6" t="n">
+      <c r="V6" t="n">
         <v>0.103394446522792</v>
       </c>
-      <c r="U6" t="n">
+      <c r="W6" t="n">
         <v>0.05614787212486128</v>
       </c>
-      <c r="V6" t="n">
+      <c r="X6" t="n">
         <v>0.04835854301095589</v>
       </c>
-      <c r="W6" t="n">
+      <c r="Y6" t="n">
         <v>0.1195036677101465</v>
       </c>
-      <c r="X6" t="n">
+      <c r="Z6" t="n">
         <v>0.09879699544698546</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="AA6" t="n">
         <v>0.0555489172844323</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="AB6" t="n">
         <v>0.09228766588138559</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AC6" t="n">
         <v>0.05189124737945493</v>
       </c>
-      <c r="AB6" t="n">
+      <c r="AD6" t="n">
         <v>0.06379366243929707</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AE6" t="n">
         <v>0.07683323011853098</v>
       </c>
-      <c r="AD6" t="n">
+      <c r="AF6" t="n">
         <v>0.07006133052072347</v>
       </c>
-      <c r="AE6" t="n">
+      <c r="AG6" t="n">
         <v>0.02758620689655172</v>
       </c>
-      <c r="AF6" t="n">
+      <c r="AH6" t="n">
         <v>0.05142377610515351</v>
       </c>
-      <c r="AG6" t="n">
+      <c r="AI6" t="n">
         <v>1.666666666666667</v>
       </c>
     </row>
@@ -1119,104 +1179,114 @@
       <c r="A7" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>106.021</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>88.89</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
         <v>79</v>
       </c>
-      <c r="C7" t="n">
+      <c r="E7" t="n">
         <v>5</v>
       </c>
-      <c r="D7" t="n">
+      <c r="F7" t="n">
         <v>16</v>
       </c>
-      <c r="E7" t="n">
+      <c r="G7" t="n">
         <v>70.03</v>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t xml:space="preserve">  As for Emily, it wasn't that simple, as nothing in life ever is.  He did mistreat her at times, and well, he did take her for granted, although she was better than anything he could ever hope for, and he could go on and on and on about all the things that went wrong.</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>milkywayoriginal_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H7" t="n">
+      <c r="J7" t="n">
         <v>0.02293790546802595</v>
       </c>
-      <c r="I7" t="n">
+      <c r="K7" t="n">
         <v>0.04487844539268827</v>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
         <v>0.03842893525614102</v>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
         <v>0.05077760950605778</v>
       </c>
-      <c r="L7" t="n">
+      <c r="N7" t="n">
         <v>0.04120249504799908</v>
       </c>
-      <c r="M7" t="n">
+      <c r="O7" t="n">
         <v>0.08159176788854362</v>
       </c>
-      <c r="N7" t="n">
+      <c r="P7" t="n">
         <v>0.07251448863799934</v>
       </c>
-      <c r="O7" t="n">
+      <c r="Q7" t="n">
         <v>0.03969292484050042</v>
       </c>
-      <c r="P7" t="n">
+      <c r="R7" t="n">
         <v>0.05009620476811044</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="S7" t="n">
         <v>0.04224651948637644</v>
       </c>
-      <c r="R7" t="n">
+      <c r="T7" t="n">
         <v>2.666666666666667</v>
       </c>
-      <c r="S7" t="n">
+      <c r="U7" t="n">
         <v>0.05610304379787563</v>
       </c>
-      <c r="T7" t="n">
+      <c r="V7" t="n">
         <v>0.1239549880803751</v>
       </c>
-      <c r="U7" t="n">
+      <c r="W7" t="n">
         <v>0.03903162055335968</v>
       </c>
-      <c r="V7" t="n">
+      <c r="X7" t="n">
         <v>0.06890973330431839</v>
       </c>
-      <c r="W7" t="n">
+      <c r="Y7" t="n">
         <v>0.07973098015631827</v>
       </c>
-      <c r="X7" t="n">
+      <c r="Z7" t="n">
         <v>0.08197668569038213</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="AA7" t="n">
         <v>0.04712561881188118</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AB7" t="n">
         <v>0.09196199501357426</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AC7" t="n">
         <v>0.03752230151650313</v>
       </c>
-      <c r="AB7" t="n">
+      <c r="AD7" t="n">
         <v>0.09320363979454889</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AE7" t="n">
         <v>0.08224378417634996</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="AF7" t="n">
         <v>0.08791208791208791</v>
       </c>
-      <c r="AE7" t="n">
+      <c r="AG7" t="n">
         <v>0.01761695906432749</v>
       </c>
-      <c r="AF7" t="n">
+      <c r="AH7" t="n">
         <v>0.04211358300142255</v>
       </c>
-      <c r="AG7" t="n">
+      <c r="AI7" t="n">
         <v>2.666666666666667</v>
       </c>
     </row>
@@ -1224,104 +1294,114 @@
       <c r="A8" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>116.877</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>106.942</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
         <v>82.39999999999999</v>
       </c>
-      <c r="C8" t="n">
+      <c r="E8" t="n">
         <v>17.6</v>
       </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
         <v>-81.26000000000001</v>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t xml:space="preserve">  But it was beside the point.  He learned his lesson, or so he told everyone, never understanding what the lesson was and how the hell was he supposed to learn it.</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>milkywayoriginal_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H8" t="n">
+      <c r="J8" t="n">
         <v>0.04285714285714286</v>
       </c>
-      <c r="I8" t="n">
+      <c r="K8" t="n">
         <v>0.0216998191681736</v>
       </c>
-      <c r="J8" t="n">
+      <c r="L8" t="n">
         <v>0.0376658753527938</v>
       </c>
-      <c r="K8" t="n">
+      <c r="M8" t="n">
         <v>0.03463885861627846</v>
       </c>
-      <c r="L8" t="n">
+      <c r="N8" t="n">
         <v>0.0198565128142593</v>
       </c>
-      <c r="M8" t="n">
+      <c r="O8" t="n">
         <v>0.06013851205277966</v>
       </c>
-      <c r="N8" t="n">
+      <c r="P8" t="n">
         <v>0.06135867241220187</v>
       </c>
-      <c r="O8" t="n">
+      <c r="Q8" t="n">
         <v>0.03580279239251689</v>
       </c>
-      <c r="P8" t="n">
+      <c r="R8" t="n">
         <v>0.0270251286996676</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="S8" t="n">
         <v>0.06696735700031289</v>
       </c>
-      <c r="R8" t="n">
+      <c r="T8" t="n">
         <v>3.5</v>
       </c>
-      <c r="S8" t="n">
+      <c r="U8" t="n">
         <v>0.08513210108604845</v>
       </c>
-      <c r="T8" t="n">
+      <c r="V8" t="n">
         <v>0.1338077866805637</v>
       </c>
-      <c r="U8" t="n">
+      <c r="W8" t="n">
         <v>0.0852935137766984</v>
       </c>
-      <c r="V8" t="n">
+      <c r="X8" t="n">
         <v>0.02941176470588236</v>
       </c>
-      <c r="W8" t="n">
+      <c r="Y8" t="n">
         <v>0.1052345807146015</v>
       </c>
-      <c r="X8" t="n">
+      <c r="Z8" t="n">
         <v>0.07480192416525185</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="AA8" t="n">
         <v>0.05302033151054833</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="AB8" t="n">
         <v>0.03933963288801998</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AC8" t="n">
         <v>0.01908396946564886</v>
       </c>
-      <c r="AB8" t="n">
+      <c r="AD8" t="n">
         <v>0.02380952380952381</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AE8" t="n">
         <v>0.09121982209385306</v>
       </c>
-      <c r="AD8" t="n">
+      <c r="AF8" t="n">
         <v>0.03944444444444444</v>
       </c>
-      <c r="AE8" t="n">
+      <c r="AG8" t="n">
         <v>0.0515878897672376</v>
       </c>
-      <c r="AF8" t="n">
+      <c r="AH8" t="n">
         <v>0.03950617283950617</v>
       </c>
-      <c r="AG8" t="n">
+      <c r="AI8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1329,104 +1409,114 @@
       <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>124.599</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>118.392</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
         <v>71.8</v>
       </c>
-      <c r="C9" t="n">
+      <c r="E9" t="n">
         <v>28.2</v>
       </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
         <v>-70.89</v>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t xml:space="preserve"> His mother recognized his regular routine and said to him impatiently, I'm so tired of you, Thomas.</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>milkywayoriginal_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H9" t="n">
+      <c r="J9" t="n">
         <v>0.0382124943000456</v>
       </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
         <v>0.04165785635092291</v>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
         <v>0.02</v>
       </c>
-      <c r="M9" t="n">
+      <c r="O9" t="n">
         <v>0.0585724888170966</v>
       </c>
-      <c r="N9" t="n">
+      <c r="P9" t="n">
         <v>0.07568545479810623</v>
       </c>
-      <c r="O9" t="n">
+      <c r="Q9" t="n">
         <v>0.00975609756097561</v>
       </c>
-      <c r="P9" t="n">
+      <c r="R9" t="n">
         <v>0.09777529404477722</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="S9" t="n">
         <v>0.0483768830152702</v>
       </c>
-      <c r="R9" t="n">
+      <c r="T9" t="n">
         <v>1.666666666666667</v>
       </c>
-      <c r="S9" t="n">
+      <c r="U9" t="n">
         <v>0.1190476190476191</v>
       </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
         <v>0.03809523809523809</v>
       </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
       <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
         <v>0.04597701149425287</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="AB9" t="n">
         <v>0.08422095615556106</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AC9" t="n">
         <v>0.08047552942923901</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AD9" t="n">
         <v>0.04744366025171301</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AE9" t="n">
         <v>0.0672328452187937</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AF9" t="n">
         <v>0.0853813813244696</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="AG9" t="n">
         <v>0.1906654741793369</v>
       </c>
-      <c r="AF9" t="n">
+      <c r="AH9" t="n">
         <v>0.04390345401581356</v>
       </c>
-      <c r="AG9" t="n">
+      <c r="AI9" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -1434,104 +1524,114 @@
       <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>131.907</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>125.22</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
         <v>67.90000000000001</v>
       </c>
-      <c r="C10" t="n">
+      <c r="E10" t="n">
         <v>13.4</v>
       </c>
-      <c r="D10" t="n">
+      <c r="F10" t="n">
         <v>18.7</v>
       </c>
-      <c r="E10" t="n">
+      <c r="G10" t="n">
         <v>39.19</v>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t xml:space="preserve">  Listen to me.  This might sound a bit wacky, but have you considered the idea of seeing a hypnotist about your broken heart?</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>milkywayoriginal_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H10" t="n">
+      <c r="J10" t="n">
         <v>0.05558124919079884</v>
       </c>
-      <c r="I10" t="n">
+      <c r="K10" t="n">
         <v>0.03946796181410888</v>
       </c>
-      <c r="J10" t="n">
+      <c r="L10" t="n">
         <v>0.03864000472098152</v>
       </c>
-      <c r="K10" t="n">
+      <c r="M10" t="n">
         <v>0.04176190476190476</v>
       </c>
-      <c r="L10" t="n">
+      <c r="N10" t="n">
         <v>0.02208269671504966</v>
       </c>
-      <c r="M10" t="n">
+      <c r="O10" t="n">
         <v>0.05072586384307991</v>
       </c>
-      <c r="N10" t="n">
+      <c r="P10" t="n">
         <v>0.05288144872545487</v>
       </c>
-      <c r="O10" t="n">
+      <c r="Q10" t="n">
         <v>0.04221866096866097</v>
       </c>
-      <c r="P10" t="n">
+      <c r="R10" t="n">
         <v>0.04947756033225316</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="S10" t="n">
         <v>0.07455066005000474</v>
       </c>
-      <c r="R10" t="n">
+      <c r="T10" t="n">
         <v>4</v>
       </c>
-      <c r="S10" t="n">
+      <c r="U10" t="n">
         <v>0.05959094033651445</v>
       </c>
-      <c r="T10" t="n">
+      <c r="V10" t="n">
         <v>0.1291252864782277</v>
       </c>
-      <c r="U10" t="n">
+      <c r="W10" t="n">
         <v>0.07864754597491171</v>
       </c>
-      <c r="V10" t="n">
+      <c r="X10" t="n">
         <v>0.07765976417092035</v>
       </c>
-      <c r="W10" t="n">
+      <c r="Y10" t="n">
         <v>0.03530512041150339</v>
       </c>
-      <c r="X10" t="n">
+      <c r="Z10" t="n">
         <v>0.03733951206215074</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="AA10" t="n">
         <v>0.02982731554160125</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="AB10" t="n">
         <v>0.03873549419767908</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AC10" t="n">
         <v>0.05400681073662131</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="AD10" t="n">
         <v>0.1111626468769326</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AE10" t="n">
         <v>0.05612244897959184</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AF10" t="n">
         <v>0.07545572004545524</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AG10" t="n">
         <v>0.05683653578390421</v>
       </c>
-      <c r="AF10" t="n">
+      <c r="AH10" t="n">
         <v>0.05433876468359227</v>
       </c>
-      <c r="AG10" t="n">
+      <c r="AI10" t="n">
         <v>2.333333333333333</v>
       </c>
     </row>
@@ -1539,104 +1639,114 @@
       <c r="A11" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>139.896</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>133.328</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
         <v>53.8</v>
       </c>
-      <c r="C11" t="n">
+      <c r="E11" t="n">
         <v>26.1</v>
       </c>
-      <c r="D11" t="n">
+      <c r="F11" t="n">
         <v>20.1</v>
       </c>
-      <c r="E11" t="n">
+      <c r="G11" t="n">
         <v>-35.32</v>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t xml:space="preserve">  Oh, Mom, that is just a stupid idea.  I'm not that desperate.  Dearest, I hope you aren't.</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>milkywayoriginal_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H11" t="n">
+      <c r="J11" t="n">
         <v>0.05793648732862484</v>
       </c>
-      <c r="I11" t="n">
+      <c r="K11" t="n">
         <v>0.02598166728601511</v>
       </c>
-      <c r="J11" t="n">
+      <c r="L11" t="n">
         <v>0.04108869272803699</v>
       </c>
-      <c r="K11" t="n">
+      <c r="M11" t="n">
         <v>0.01858108108108108</v>
       </c>
-      <c r="L11" t="n">
+      <c r="N11" t="n">
         <v>0.03890285795233205</v>
       </c>
-      <c r="M11" t="n">
+      <c r="O11" t="n">
         <v>0.0078125</v>
       </c>
-      <c r="N11" t="n">
+      <c r="P11" t="n">
         <v>0.04545454545454546</v>
       </c>
-      <c r="O11" t="n">
+      <c r="Q11" t="n">
         <v>0.03469995419147962</v>
       </c>
-      <c r="P11" t="n">
+      <c r="R11" t="n">
         <v>0.03435534591194969</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="S11" t="n">
         <v>0.05915178571428571</v>
       </c>
-      <c r="R11" t="n">
+      <c r="T11" t="n">
         <v>1.333333333333333</v>
       </c>
-      <c r="S11" t="n">
+      <c r="U11" t="n">
         <v>0.1193759071117562</v>
       </c>
-      <c r="T11" t="n">
+      <c r="V11" t="n">
         <v>0.1617647058823529</v>
       </c>
-      <c r="U11" t="n">
+      <c r="W11" t="n">
         <v>0.06521739130434782</v>
       </c>
-      <c r="V11" t="n">
+      <c r="X11" t="n">
         <v>0.1676329976604618</v>
       </c>
-      <c r="W11" t="n">
+      <c r="Y11" t="n">
         <v>0.0794451450189155</v>
       </c>
-      <c r="X11" t="n">
+      <c r="Z11" t="n">
         <v>0.03012048192771084</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="AA11" t="n">
         <v>0.05171703296703296</v>
       </c>
-      <c r="Z11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0</v>
-      </c>
       <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
         <v>0.09740259740259741</v>
       </c>
-      <c r="AC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0</v>
-      </c>
       <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
         <v>0.05263157894736842</v>
       </c>
-      <c r="AF11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="n">
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -1644,104 +1754,114 @@
       <c r="A12" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>154.125</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>141.437</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
         <v>70.89999999999999</v>
       </c>
-      <c r="C12" t="n">
+      <c r="E12" t="n">
         <v>19.3</v>
       </c>
-      <c r="D12" t="n">
+      <c r="F12" t="n">
         <v>9.9</v>
       </c>
-      <c r="E12" t="n">
+      <c r="G12" t="n">
         <v>-64.28</v>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t xml:space="preserve">  He sometimes hated his mom for her brutal honesty, but she had a point.  Okay, Mom, I'll look into it, he said mechanically as he hung up and thought to himself, What do I have to lose?</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>milkywayoriginal_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H12" t="n">
+      <c r="J12" t="n">
         <v>0.015625</v>
       </c>
-      <c r="I12" t="n">
+      <c r="K12" t="n">
         <v>0.0130006767330711</v>
       </c>
-      <c r="J12" t="n">
+      <c r="L12" t="n">
         <v>0.03150526302010771</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
         <v>0.009178321678321678</v>
       </c>
-      <c r="M12" t="n">
+      <c r="O12" t="n">
         <v>0.08181514319460537</v>
       </c>
-      <c r="N12" t="n">
+      <c r="P12" t="n">
         <v>0.04935929775906439</v>
       </c>
-      <c r="O12" t="n">
+      <c r="Q12" t="n">
         <v>0.05110097059249601</v>
       </c>
-      <c r="P12" t="n">
+      <c r="R12" t="n">
         <v>0.06494197545311504</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="S12" t="n">
         <v>0.08882969798638694</v>
       </c>
-      <c r="R12" t="n">
+      <c r="T12" t="n">
         <v>1.6</v>
       </c>
-      <c r="S12" t="n">
+      <c r="U12" t="n">
         <v>0.05602938644320725</v>
       </c>
-      <c r="T12" t="n">
+      <c r="V12" t="n">
         <v>0.02204724409448819</v>
       </c>
-      <c r="U12" t="n">
+      <c r="W12" t="n">
         <v>0.04014388489208633</v>
       </c>
-      <c r="V12" t="n">
+      <c r="X12" t="n">
         <v>0.04147058823529411</v>
       </c>
-      <c r="W12" t="n">
+      <c r="Y12" t="n">
         <v>0.04176445023902651</v>
       </c>
-      <c r="X12" t="n">
+      <c r="Z12" t="n">
         <v>0.01886792452830189</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="AA12" t="n">
         <v>0.04573209999414554</v>
       </c>
-      <c r="Z12" t="n">
+      <c r="AB12" t="n">
         <v>0.11606682559487</v>
       </c>
-      <c r="AA12" t="n">
+      <c r="AC12" t="n">
         <v>0.1304026972096824</v>
       </c>
-      <c r="AB12" t="n">
+      <c r="AD12" t="n">
         <v>0.08296610053045025</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AE12" t="n">
         <v>0.05710653911934714</v>
       </c>
-      <c r="AD12" t="n">
+      <c r="AF12" t="n">
         <v>0.09761811212736131</v>
       </c>
-      <c r="AE12" t="n">
+      <c r="AG12" t="n">
         <v>0.09568494764618207</v>
       </c>
-      <c r="AF12" t="n">
+      <c r="AH12" t="n">
         <v>0.06496641103382676</v>
       </c>
-      <c r="AG12" t="n">
+      <c r="AI12" t="n">
         <v>0.625</v>
       </c>
     </row>
@@ -1749,73 +1869,77 @@
       <c r="A13" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>163.014</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>156.488</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
         <v>73.2</v>
       </c>
-      <c r="C13" t="n">
+      <c r="E13" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="D13" t="n">
+      <c r="F13" t="n">
         <v>17.1</v>
       </c>
-      <c r="E13" t="n">
+      <c r="G13" t="n">
         <v>42.15</v>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t xml:space="preserve"> He woke up early the next morning and frantically scanned the web for the combination of best and cheapest therapist.</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>milkywayoriginal_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
         <v>0.04651162790697674</v>
       </c>
-      <c r="J13" t="n">
+      <c r="L13" t="n">
         <v>0.03041362530413626</v>
       </c>
-      <c r="K13" t="n">
+      <c r="M13" t="n">
         <v>0.08690671031096563</v>
       </c>
-      <c r="L13" t="n">
+      <c r="N13" t="n">
         <v>0.03278688524590163</v>
       </c>
-      <c r="M13" t="n">
+      <c r="O13" t="n">
         <v>0.0189873417721519</v>
       </c>
-      <c r="N13" t="n">
+      <c r="P13" t="n">
         <v>0.0213903743315508</v>
       </c>
-      <c r="O13" t="n">
+      <c r="Q13" t="n">
         <v>0.04081632653061223</v>
       </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
         <v>0.02173913043478261</v>
       </c>
-      <c r="R13" t="n">
+      <c r="T13" t="n">
         <v>0.25</v>
       </c>
-      <c r="S13" t="n">
+      <c r="U13" t="n">
         <v>0.04</v>
       </c>
-      <c r="T13" t="n">
+      <c r="V13" t="n">
         <v>0.05202312138728324</v>
       </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
@@ -1823,30 +1947,36 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
         <v>0.02752293577981652</v>
       </c>
-      <c r="Z13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0</v>
-      </c>
       <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
         <v>0.06875000000000001</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AE13" t="n">
         <v>0.08496732026143791</v>
       </c>
-      <c r="AD13" t="n">
+      <c r="AF13" t="n">
         <v>0.06451612903225806</v>
       </c>
-      <c r="AE13" t="n">
+      <c r="AG13" t="n">
         <v>0.05042016806722689</v>
       </c>
-      <c r="AF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="n">
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
         <v>0.1111111111111111</v>
       </c>
     </row>
@@ -1854,104 +1984,114 @@
       <c r="A14" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>170.462</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>164.155</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
         <v>77.2</v>
       </c>
-      <c r="C14" t="n">
+      <c r="E14" t="n">
         <v>5.7</v>
       </c>
-      <c r="D14" t="n">
+      <c r="F14" t="n">
         <v>17.1</v>
       </c>
-      <c r="E14" t="n">
+      <c r="G14" t="n">
         <v>58.59</v>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t xml:space="preserve"> Before long, he understood that, knowing nothing about the subject, it was hard to figure out which therapist was the best.</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>milkywayoriginal_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H14" t="n">
+      <c r="J14" t="n">
         <v>0.02811584403876493</v>
       </c>
-      <c r="I14" t="n">
+      <c r="K14" t="n">
         <v>0.05964213754137709</v>
       </c>
-      <c r="J14" t="n">
+      <c r="L14" t="n">
         <v>0.0483124908585637</v>
       </c>
-      <c r="K14" t="n">
+      <c r="M14" t="n">
         <v>0.02439024390243902</v>
       </c>
-      <c r="L14" t="n">
+      <c r="N14" t="n">
         <v>0.01709401709401709</v>
       </c>
-      <c r="M14" t="n">
+      <c r="O14" t="n">
         <v>0.06154616017184733</v>
       </c>
-      <c r="N14" t="n">
+      <c r="P14" t="n">
         <v>0.04640023315282791</v>
       </c>
-      <c r="O14" t="n">
+      <c r="Q14" t="n">
         <v>0.05500509911868526</v>
       </c>
-      <c r="P14" t="n">
+      <c r="R14" t="n">
         <v>0.07987952217279405</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="S14" t="n">
         <v>0.06390556255718637</v>
       </c>
-      <c r="R14" t="n">
+      <c r="T14" t="n">
         <v>3</v>
       </c>
-      <c r="S14" t="n">
+      <c r="U14" t="n">
         <v>0.1047248803827751</v>
       </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
         <v>0.08732558139534885</v>
       </c>
-      <c r="V14" t="n">
+      <c r="X14" t="n">
         <v>0.1087914023960536</v>
       </c>
-      <c r="W14" t="n">
+      <c r="Y14" t="n">
         <v>0.1090025457070123</v>
       </c>
-      <c r="X14" t="n">
+      <c r="Z14" t="n">
         <v>0.05965532479010163</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="AA14" t="n">
         <v>0.02649006622516556</v>
       </c>
-      <c r="Z14" t="n">
+      <c r="AB14" t="n">
         <v>0.09166022419791264</v>
       </c>
-      <c r="AA14" t="n">
+      <c r="AC14" t="n">
         <v>0.1615316316118627</v>
       </c>
-      <c r="AB14" t="n">
+      <c r="AD14" t="n">
         <v>0.09785289424053387</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="AE14" t="n">
         <v>0.06419457735247208</v>
       </c>
-      <c r="AD14" t="n">
+      <c r="AF14" t="n">
         <v>0.1035137701804368</v>
       </c>
-      <c r="AE14" t="n">
+      <c r="AG14" t="n">
         <v>0.03246753246753246</v>
       </c>
-      <c r="AF14" t="n">
+      <c r="AH14" t="n">
         <v>0.0297661233167966</v>
       </c>
-      <c r="AG14" t="n">
+      <c r="AI14" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1959,85 +2099,89 @@
       <c r="A15" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>179.117</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>171.162</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
         <v>100</v>
       </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="inlineStr">
         <is>
           <t xml:space="preserve">  He would have to settle for the cheapest one he could find.  Andre the Giant, chiropractor and hypnosis therapist, money back guaranteed.</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>milkywayoriginal_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
       <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
         <v>0.03968253968253969</v>
       </c>
-      <c r="K15" t="n">
+      <c r="M15" t="n">
         <v>0.03467297084318361</v>
       </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
         <v>0.07954038032181077</v>
       </c>
-      <c r="N15" t="n">
+      <c r="P15" t="n">
         <v>0.2264850307727209</v>
       </c>
-      <c r="O15" t="n">
+      <c r="Q15" t="n">
         <v>0.02666666666666667</v>
       </c>
-      <c r="P15" t="n">
+      <c r="R15" t="n">
         <v>0.05792682926829268</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="S15" t="n">
         <v>0.1032804232804233</v>
       </c>
-      <c r="R15" t="n">
+      <c r="T15" t="n">
         <v>0.5</v>
       </c>
-      <c r="S15" t="n">
+      <c r="U15" t="n">
         <v>0.3364485981308411</v>
       </c>
-      <c r="T15" t="n">
+      <c r="V15" t="n">
         <v>0.2275132275132275</v>
       </c>
-      <c r="U15" t="n">
+      <c r="W15" t="n">
         <v>0.1888888888888889</v>
       </c>
-      <c r="V15" t="n">
+      <c r="X15" t="n">
         <v>0.09424083769633508</v>
       </c>
-      <c r="W15" t="n">
+      <c r="Y15" t="n">
         <v>0.2666666666666667</v>
       </c>
-      <c r="X15" t="n">
+      <c r="Z15" t="n">
         <v>0.145985401459854</v>
       </c>
-      <c r="Y15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0</v>
-      </c>
       <c r="AA15" t="n">
         <v>0</v>
       </c>
@@ -2054,9 +2198,15 @@
         <v>0</v>
       </c>
       <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
         <v>0.3779069767441861</v>
       </c>
-      <c r="AG15" t="n">
+      <c r="AI15" t="n">
         <v>0.125</v>
       </c>
     </row>
@@ -2064,104 +2214,114 @@
       <c r="A16" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>188.306</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>179.978</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
         <v>71.09999999999999</v>
       </c>
-      <c r="C16" t="n">
+      <c r="E16" t="n">
         <v>4.9</v>
       </c>
-      <c r="D16" t="n">
+      <c r="F16" t="n">
         <v>24</v>
       </c>
-      <c r="E16" t="n">
+      <c r="G16" t="n">
         <v>81.59999999999999</v>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t xml:space="preserve"> The combination was a bit odd, but just the thought of Princess Bride, which was his all-time favorite movie by far, made the choice so much easier.</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>milkywayoriginal_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H16" t="n">
+      <c r="J16" t="n">
         <v>0.02</v>
       </c>
-      <c r="I16" t="n">
+      <c r="K16" t="n">
         <v>0.05710098182047901</v>
       </c>
-      <c r="J16" t="n">
+      <c r="L16" t="n">
         <v>0.0703301025312574</v>
       </c>
-      <c r="K16" t="n">
+      <c r="M16" t="n">
         <v>0.04552475450081833</v>
       </c>
-      <c r="L16" t="n">
+      <c r="N16" t="n">
         <v>0.0241948842018612</v>
       </c>
-      <c r="M16" t="n">
+      <c r="O16" t="n">
         <v>0.04806268713336286</v>
       </c>
-      <c r="N16" t="n">
+      <c r="P16" t="n">
         <v>0.03678093363745988</v>
       </c>
-      <c r="O16" t="n">
+      <c r="Q16" t="n">
         <v>0.01853741496598639</v>
       </c>
-      <c r="P16" t="n">
+      <c r="R16" t="n">
         <v>0.03841121676635268</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="S16" t="n">
         <v>0.03468469841437005</v>
       </c>
-      <c r="R16" t="n">
+      <c r="T16" t="n">
         <v>2</v>
       </c>
-      <c r="S16" t="n">
+      <c r="U16" t="n">
         <v>0.02978723404255319</v>
       </c>
-      <c r="T16" t="n">
+      <c r="V16" t="n">
         <v>0.1090161627361508</v>
       </c>
-      <c r="U16" t="n">
+      <c r="W16" t="n">
         <v>0.05700374531835206</v>
       </c>
-      <c r="V16" t="n">
+      <c r="X16" t="n">
         <v>0.05576450614201538</v>
       </c>
-      <c r="W16" t="n">
+      <c r="Y16" t="n">
         <v>0.08942961800104657</v>
       </c>
-      <c r="X16" t="n">
+      <c r="Z16" t="n">
         <v>0.08237273630644426</v>
       </c>
-      <c r="Y16" t="n">
+      <c r="AA16" t="n">
         <v>0.03783251231527094</v>
       </c>
-      <c r="Z16" t="n">
+      <c r="AB16" t="n">
         <v>0.1452573647944456</v>
       </c>
-      <c r="AA16" t="n">
+      <c r="AC16" t="n">
         <v>0.07619450317124736</v>
       </c>
-      <c r="AB16" t="n">
+      <c r="AD16" t="n">
         <v>0.1038668082290849</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AE16" t="n">
         <v>0.01806451612903226</v>
       </c>
-      <c r="AD16" t="n">
+      <c r="AF16" t="n">
         <v>0.06358279401757663</v>
       </c>
-      <c r="AE16" t="n">
+      <c r="AG16" t="n">
         <v>0.03582089552238805</v>
       </c>
-      <c r="AF16" t="n">
+      <c r="AH16" t="n">
         <v>0.04011815496478073</v>
       </c>
-      <c r="AG16" t="n">
+      <c r="AI16" t="n">
         <v>0.7142857142857143</v>
       </c>
     </row>
@@ -2169,104 +2329,114 @@
       <c r="A17" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>196.254</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>188.346</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
         <v>56.49999999999999</v>
       </c>
-      <c r="C17" t="n">
+      <c r="E17" t="n">
         <v>21</v>
       </c>
-      <c r="D17" t="n">
+      <c r="F17" t="n">
         <v>22.6</v>
       </c>
-      <c r="E17" t="n">
+      <c r="G17" t="n">
         <v>10.27</v>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t xml:space="preserve">  A low voice answered his call.  It's your lucky day, Mr. Smith.  Somehow a fake name felt safer.</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>milkywayoriginal_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H17" t="n">
+      <c r="J17" t="n">
         <v>0.02285714285714285</v>
       </c>
-      <c r="I17" t="n">
+      <c r="K17" t="n">
         <v>0.0161764705882353</v>
       </c>
-      <c r="J17" t="n">
+      <c r="L17" t="n">
         <v>0.02637362637362637</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
         <v>0.01647058823529412</v>
       </c>
-      <c r="M17" t="n">
+      <c r="O17" t="n">
         <v>0.09565185779708858</v>
       </c>
-      <c r="N17" t="n">
+      <c r="P17" t="n">
         <v>0.1370252385719063</v>
       </c>
-      <c r="O17" t="n">
+      <c r="Q17" t="n">
         <v>0.06235209635154203</v>
       </c>
-      <c r="P17" t="n">
+      <c r="R17" t="n">
         <v>0.0708374029428671</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="S17" t="n">
         <v>0.09367660362828616</v>
       </c>
-      <c r="R17" t="n">
+      <c r="T17" t="n">
         <v>1</v>
       </c>
-      <c r="S17" t="n">
+      <c r="U17" t="n">
         <v>0.0859375</v>
       </c>
-      <c r="T17" t="n">
+      <c r="V17" t="n">
         <v>0.05696202531645569</v>
       </c>
-      <c r="U17" t="n">
+      <c r="W17" t="n">
         <v>0.0824319855461724</v>
       </c>
-      <c r="V17" t="n">
+      <c r="X17" t="n">
         <v>0.05660377358490566</v>
       </c>
-      <c r="W17" t="n">
+      <c r="Y17" t="n">
         <v>0.02706109134045077</v>
       </c>
-      <c r="X17" t="n">
+      <c r="Z17" t="n">
         <v>0.07239665096807954</v>
       </c>
-      <c r="Y17" t="n">
+      <c r="AA17" t="n">
         <v>0.007683169834457388</v>
       </c>
-      <c r="Z17" t="n">
+      <c r="AB17" t="n">
         <v>0.2420192372823952</v>
       </c>
-      <c r="AA17" t="n">
+      <c r="AC17" t="n">
         <v>0.1152016625615764</v>
       </c>
-      <c r="AB17" t="n">
+      <c r="AD17" t="n">
         <v>0.01666666666666667</v>
       </c>
-      <c r="AC17" t="n">
+      <c r="AE17" t="n">
         <v>0.09610329466766639</v>
       </c>
-      <c r="AD17" t="n">
+      <c r="AF17" t="n">
         <v>0.1323489198796828</v>
       </c>
-      <c r="AE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="n">
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
         <v>0.06192129629629629</v>
       </c>
-      <c r="AG17" t="n">
+      <c r="AI17" t="n">
         <v>0.6666666666666666</v>
       </c>
     </row>
@@ -2274,104 +2444,114 @@
       <c r="A18" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B18" t="n">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>203.361</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>197.155</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
         <v>85.59999999999999</v>
       </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
         <v>14.4</v>
       </c>
-      <c r="E18" t="n">
+      <c r="G18" t="n">
         <v>52.16</v>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t xml:space="preserve"> I have a cancellation for 10.15 a.m. today, but it's going to be chilly, so be sure to wear a scarf.</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>milkywayoriginal_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H18" t="n">
+      <c r="J18" t="n">
         <v>0.07592729059199214</v>
       </c>
-      <c r="I18" t="n">
+      <c r="K18" t="n">
         <v>0.1196903958433767</v>
       </c>
-      <c r="J18" t="n">
+      <c r="L18" t="n">
         <v>0.06212626894729523</v>
       </c>
-      <c r="K18" t="n">
+      <c r="M18" t="n">
         <v>0.07352941176470588</v>
       </c>
-      <c r="L18" t="n">
+      <c r="N18" t="n">
         <v>0.09109187866072209</v>
       </c>
-      <c r="M18" t="n">
+      <c r="O18" t="n">
         <v>0.04034690799396682</v>
       </c>
-      <c r="N18" t="n">
+      <c r="P18" t="n">
         <v>0.03169627307558342</v>
       </c>
-      <c r="O18" t="n">
+      <c r="Q18" t="n">
         <v>0.04157386785449147</v>
       </c>
-      <c r="P18" t="n">
+      <c r="R18" t="n">
         <v>0.03237282106012096</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="S18" t="n">
         <v>0.03312629399585921</v>
       </c>
-      <c r="R18" t="n">
+      <c r="T18" t="n">
         <v>0.6</v>
       </c>
-      <c r="S18" t="n">
+      <c r="U18" t="n">
         <v>0.1819845027981059</v>
       </c>
-      <c r="T18" t="n">
+      <c r="V18" t="n">
         <v>0.07291666666666667</v>
       </c>
-      <c r="U18" t="n">
+      <c r="W18" t="n">
         <v>0.1071428571428571</v>
       </c>
-      <c r="V18" t="n">
+      <c r="X18" t="n">
         <v>0.1290322580645161</v>
       </c>
-      <c r="W18" t="n">
+      <c r="Y18" t="n">
         <v>0.1886102403343783</v>
       </c>
-      <c r="X18" t="n">
+      <c r="Z18" t="n">
         <v>0.1493146891873183</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="AA18" t="n">
         <v>0.02439024390243903</v>
       </c>
-      <c r="Z18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="n">
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
         <v>0.09328358208955224</v>
       </c>
-      <c r="AB18" t="n">
+      <c r="AD18" t="n">
         <v>0.1024464831804281</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="AE18" t="n">
         <v>0.08787878787878788</v>
       </c>
-      <c r="AD18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>0</v>
-      </c>
       <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
         <v>0.05204460966542751</v>
       </c>
-      <c r="AG18" t="n">
+      <c r="AI18" t="n">
         <v>0.3333333333333333</v>
       </c>
     </row>
@@ -2379,104 +2559,114 @@
       <c r="A19" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="B19" t="n">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>213.411</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>204.742</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
         <v>69.5</v>
       </c>
-      <c r="C19" t="n">
+      <c r="E19" t="n">
         <v>12.7</v>
       </c>
-      <c r="D19" t="n">
+      <c r="F19" t="n">
         <v>17.8</v>
       </c>
-      <c r="E19" t="n">
+      <c r="G19" t="n">
         <v>7.720000000000001</v>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t xml:space="preserve"> He arrived at Andre's clinic at 9.56, and Andre, who to his disappointment was a surprisingly short giant, welcomed him in.</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>milkywayoriginal_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H19" t="n">
+      <c r="J19" t="n">
         <v>0.108974358974359</v>
       </c>
-      <c r="I19" t="n">
+      <c r="K19" t="n">
         <v>0.02451664341239784</v>
       </c>
-      <c r="J19" t="n">
+      <c r="L19" t="n">
         <v>0.09333927510398099</v>
       </c>
-      <c r="K19" t="n">
+      <c r="M19" t="n">
         <v>0.04054054054054054</v>
       </c>
-      <c r="L19" t="n">
+      <c r="N19" t="n">
         <v>0.05103686635944701</v>
       </c>
-      <c r="M19" t="n">
+      <c r="O19" t="n">
         <v>0.04648617511520738</v>
       </c>
-      <c r="N19" t="n">
+      <c r="P19" t="n">
         <v>0.0499727668845316</v>
       </c>
-      <c r="O19" t="n">
+      <c r="Q19" t="n">
         <v>0.02</v>
       </c>
-      <c r="P19" t="n">
+      <c r="R19" t="n">
         <v>0.04737903225806452</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="S19" t="n">
         <v>0.03627694859038143</v>
       </c>
-      <c r="R19" t="n">
+      <c r="T19" t="n">
         <v>0.8</v>
       </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
       <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
         <v>0.04629629629629629</v>
       </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
         <v>0.03448275862068965</v>
       </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0</v>
-      </c>
       <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
         <v>0.1458333333333333</v>
       </c>
-      <c r="AA19" t="n">
+      <c r="AC19" t="n">
         <v>0.1857945425361155</v>
       </c>
-      <c r="AB19" t="n">
+      <c r="AD19" t="n">
         <v>0.02</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AE19" t="n">
         <v>0.1407103825136612</v>
       </c>
-      <c r="AD19" t="n">
+      <c r="AF19" t="n">
         <v>0.07407407407407407</v>
       </c>
-      <c r="AE19" t="n">
+      <c r="AG19" t="n">
         <v>0.02727272727272727</v>
       </c>
-      <c r="AF19" t="n">
+      <c r="AH19" t="n">
         <v>0.0982615268329554</v>
       </c>
-      <c r="AG19" t="n">
+      <c r="AI19" t="n">
         <v>0.2857142857142857</v>
       </c>
     </row>
@@ -2484,104 +2674,114 @@
       <c r="A20" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="B20" t="n">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>221.138</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>214.412</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
         <v>61.1</v>
       </c>
-      <c r="C20" t="n">
+      <c r="E20" t="n">
         <v>38.9</v>
       </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
         <v>-79.06</v>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t xml:space="preserve">  I hate Wednesdays, he said.  For some reason, everyone seems to be sick.</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>milkywayoriginal_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
       <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
         <v>0.03588982218981378</v>
       </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
       <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
         <v>0.1127072005129602</v>
       </c>
-      <c r="N20" t="n">
+      <c r="P20" t="n">
         <v>0.1029578276543046</v>
       </c>
-      <c r="O20" t="n">
+      <c r="Q20" t="n">
         <v>0.05355949197860962</v>
       </c>
-      <c r="P20" t="n">
+      <c r="R20" t="n">
         <v>0.08662860568676761</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="S20" t="n">
         <v>0.09856707048365129</v>
       </c>
-      <c r="R20" t="n">
+      <c r="T20" t="n">
         <v>4</v>
       </c>
-      <c r="S20" t="n">
+      <c r="U20" t="n">
         <v>0.01893939393939394</v>
       </c>
-      <c r="T20" t="n">
+      <c r="V20" t="n">
         <v>0.01470588235294118</v>
       </c>
-      <c r="U20" t="n">
+      <c r="W20" t="n">
         <v>0.02016129032258064</v>
       </c>
-      <c r="V20" t="n">
+      <c r="X20" t="n">
         <v>0.01271186440677966</v>
       </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
         <v>0.03</v>
       </c>
-      <c r="Y20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="n">
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
         <v>0.2182606222115759</v>
       </c>
-      <c r="AA20" t="n">
+      <c r="AC20" t="n">
         <v>0.09124467795996014</v>
       </c>
-      <c r="AB20" t="n">
+      <c r="AD20" t="n">
         <v>0.1435921193271911</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AE20" t="n">
         <v>0.1178812095964774</v>
       </c>
-      <c r="AD20" t="n">
+      <c r="AF20" t="n">
         <v>0.148160832598908</v>
       </c>
-      <c r="AE20" t="n">
+      <c r="AG20" t="n">
         <v>0.1237314958496515</v>
       </c>
-      <c r="AF20" t="n">
+      <c r="AH20" t="n">
         <v>0.04901104409531376</v>
       </c>
-      <c r="AG20" t="n">
+      <c r="AI20" t="n">
         <v>4</v>
       </c>
     </row>
@@ -2589,104 +2789,114 @@
       <c r="A21" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>233.17</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>221.158</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
         <v>89.3</v>
       </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
         <v>10.7</v>
       </c>
-      <c r="E21" t="n">
+      <c r="G21" t="n">
         <v>49.39</v>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t xml:space="preserve">  I know what you mean.  I used to be in the toilet paper industry, Thomas replied, feeling that was an eccentric response.  So, are you interested in chiropractic therapy, or are you here just for hypnosis session?</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>milkywayoriginal_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H21" t="n">
+      <c r="J21" t="n">
         <v>0.0243969298245614</v>
       </c>
-      <c r="I21" t="n">
+      <c r="K21" t="n">
         <v>0.02824349124175714</v>
       </c>
-      <c r="J21" t="n">
+      <c r="L21" t="n">
         <v>0.04283999186477472</v>
       </c>
-      <c r="K21" t="n">
+      <c r="M21" t="n">
         <v>0.04833004332721393</v>
       </c>
-      <c r="L21" t="n">
+      <c r="N21" t="n">
         <v>0.04665754919486263</v>
       </c>
-      <c r="M21" t="n">
+      <c r="O21" t="n">
         <v>0.08273943721822935</v>
       </c>
-      <c r="N21" t="n">
+      <c r="P21" t="n">
         <v>0.04652315999229379</v>
       </c>
-      <c r="O21" t="n">
+      <c r="Q21" t="n">
         <v>0.03973063973063973</v>
       </c>
-      <c r="P21" t="n">
+      <c r="R21" t="n">
         <v>0.01176528641317374</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="S21" t="n">
         <v>0.03475960838346159</v>
       </c>
-      <c r="R21" t="n">
+      <c r="T21" t="n">
         <v>1.5</v>
       </c>
-      <c r="S21" t="n">
+      <c r="U21" t="n">
         <v>0.06431334622823985</v>
       </c>
-      <c r="T21" t="n">
+      <c r="V21" t="n">
         <v>0.02571428571428571</v>
       </c>
-      <c r="U21" t="n">
+      <c r="W21" t="n">
         <v>0.06507063749853245</v>
       </c>
-      <c r="V21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" t="n">
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
         <v>0.06483957219251338</v>
       </c>
-      <c r="X21" t="n">
+      <c r="Z21" t="n">
         <v>0.04597739922415247</v>
       </c>
-      <c r="Y21" t="n">
+      <c r="AA21" t="n">
         <v>0.01818181818181818</v>
       </c>
-      <c r="Z21" t="n">
+      <c r="AB21" t="n">
         <v>0.1195934500282327</v>
       </c>
-      <c r="AA21" t="n">
+      <c r="AC21" t="n">
         <v>0.1282217544566942</v>
       </c>
-      <c r="AB21" t="n">
+      <c r="AD21" t="n">
         <v>0.05374201787994892</v>
       </c>
-      <c r="AC21" t="n">
+      <c r="AE21" t="n">
         <v>0.09380700131664411</v>
       </c>
-      <c r="AD21" t="n">
+      <c r="AF21" t="n">
         <v>0.1002601976450799</v>
       </c>
-      <c r="AE21" t="n">
+      <c r="AG21" t="n">
         <v>0.0598936170212766</v>
       </c>
-      <c r="AF21" t="n">
+      <c r="AH21" t="n">
         <v>0.06742583028297314</v>
       </c>
-      <c r="AG21" t="n">
+      <c r="AI21" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -2694,104 +2904,114 @@
       <c r="A22" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="B22" t="n">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>240.51</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>233.671</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
         <v>80.7</v>
       </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
         <v>19.3</v>
       </c>
-      <c r="E22" t="n">
+      <c r="G22" t="n">
         <v>51.06</v>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t xml:space="preserve">  Andre asked.  Just the hypnosis session.  My back seems to be just fine these days, thank you, Thomas said assertively.</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>milkywayoriginal_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H22" t="n">
+      <c r="J22" t="n">
         <v>0.02731259968102073</v>
       </c>
-      <c r="I22" t="n">
+      <c r="K22" t="n">
         <v>0.02709606066989678</v>
       </c>
-      <c r="J22" t="n">
+      <c r="L22" t="n">
         <v>0.05764600942080374</v>
       </c>
-      <c r="K22" t="n">
+      <c r="M22" t="n">
         <v>0.05687645687645689</v>
       </c>
-      <c r="L22" t="n">
+      <c r="N22" t="n">
         <v>0.015</v>
       </c>
-      <c r="M22" t="n">
+      <c r="O22" t="n">
         <v>0.025206492257535</v>
       </c>
-      <c r="N22" t="n">
+      <c r="P22" t="n">
         <v>0.01182221211776742</v>
       </c>
-      <c r="O22" t="n">
+      <c r="Q22" t="n">
         <v>0.01645569620253165</v>
       </c>
-      <c r="P22" t="n">
+      <c r="R22" t="n">
         <v>0.01137129380053908</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="S22" t="n">
         <v>0.01893241612376964</v>
       </c>
-      <c r="R22" t="n">
+      <c r="T22" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
       <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
         <v>0.06976744186046512</v>
       </c>
-      <c r="V22" t="n">
+      <c r="X22" t="n">
         <v>0.0379746835443038</v>
       </c>
-      <c r="W22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" t="n">
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
         <v>0.0514018691588785</v>
       </c>
-      <c r="Y22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z22" t="n">
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
         <v>0.1173432472790529</v>
       </c>
-      <c r="AA22" t="n">
+      <c r="AC22" t="n">
         <v>0.0919882340051858</v>
       </c>
-      <c r="AB22" t="n">
+      <c r="AD22" t="n">
         <v>0.04338771259979174</v>
       </c>
-      <c r="AC22" t="n">
+      <c r="AE22" t="n">
         <v>0.03931080628972901</v>
       </c>
-      <c r="AD22" t="n">
+      <c r="AF22" t="n">
         <v>0.09765531892844188</v>
       </c>
-      <c r="AE22" t="n">
+      <c r="AG22" t="n">
         <v>0.02737752161383285</v>
       </c>
-      <c r="AF22" t="n">
+      <c r="AH22" t="n">
         <v>0.05032811549665482</v>
       </c>
-      <c r="AG22" t="n">
+      <c r="AI22" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -2799,104 +3019,114 @@
       <c r="A23" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="B23" t="n">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>247.622</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>241.171</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
         <v>71</v>
       </c>
-      <c r="C23" t="n">
+      <c r="E23" t="n">
         <v>15.4</v>
       </c>
-      <c r="D23" t="n">
+      <c r="F23" t="n">
         <v>13.6</v>
       </c>
-      <c r="E23" t="n">
+      <c r="G23" t="n">
         <v>-7.720000000000001</v>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t xml:space="preserve">  Sure, man, Andre replied and coughed.  What seems to be bothering you, Mr. Smith?</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>milkywayoriginal_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H23" t="n">
+      <c r="J23" t="n">
         <v>0.04202898550724637</v>
       </c>
-      <c r="I23" t="n">
+      <c r="K23" t="n">
         <v>0.03805774278215223</v>
       </c>
-      <c r="J23" t="n">
+      <c r="L23" t="n">
         <v>0.04084967320261437</v>
       </c>
-      <c r="K23" t="n">
+      <c r="M23" t="n">
         <v>0.04131652661064426</v>
       </c>
-      <c r="L23" t="n">
+      <c r="N23" t="n">
         <v>0.04569892473118279</v>
       </c>
-      <c r="M23" t="n">
+      <c r="O23" t="n">
         <v>0.1233872859488623</v>
       </c>
-      <c r="N23" t="n">
+      <c r="P23" t="n">
         <v>0.05217771419488158</v>
       </c>
-      <c r="O23" t="n">
+      <c r="Q23" t="n">
         <v>0.06158651982579749</v>
       </c>
-      <c r="P23" t="n">
+      <c r="R23" t="n">
         <v>0.05055292259083729</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="S23" t="n">
         <v>0.04556962025316456</v>
       </c>
-      <c r="R23" t="n">
+      <c r="T23" t="n">
         <v>0.6</v>
       </c>
-      <c r="S23" t="n">
+      <c r="U23" t="n">
         <v>0.08415841584158416</v>
       </c>
-      <c r="T23" t="n">
+      <c r="V23" t="n">
         <v>0.07291666666666667</v>
       </c>
-      <c r="U23" t="n">
+      <c r="W23" t="n">
         <v>0.1071428571428571</v>
       </c>
-      <c r="V23" t="n">
+      <c r="X23" t="n">
         <v>0.1290322580645161</v>
       </c>
-      <c r="W23" t="n">
+      <c r="Y23" t="n">
         <v>0.09090909090909091</v>
       </c>
-      <c r="X23" t="n">
+      <c r="Z23" t="n">
         <v>0.08064516129032258</v>
       </c>
-      <c r="Y23" t="n">
+      <c r="AA23" t="n">
         <v>0.02439024390243903</v>
       </c>
-      <c r="Z23" t="n">
+      <c r="AB23" t="n">
         <v>0.06907894736842106</v>
       </c>
-      <c r="AA23" t="n">
+      <c r="AC23" t="n">
         <v>0.1366279069767442</v>
       </c>
-      <c r="AB23" t="n">
+      <c r="AD23" t="n">
         <v>0.08544303797468354</v>
       </c>
-      <c r="AC23" t="n">
+      <c r="AE23" t="n">
         <v>0.07228915662650602</v>
       </c>
-      <c r="AD23" t="n">
+      <c r="AF23" t="n">
         <v>0.08064516129032258</v>
       </c>
-      <c r="AE23" t="n">
+      <c r="AG23" t="n">
         <v>0.0641025641025641</v>
       </c>
-      <c r="AF23" t="n">
+      <c r="AH23" t="n">
         <v>0.072992700729927</v>
       </c>
-      <c r="AG23" t="n">
+      <c r="AI23" t="n">
         <v>0.3333333333333333</v>
       </c>
     </row>
@@ -2904,104 +3134,114 @@
       <c r="A24" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="B24" t="n">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>253.893</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>247.682</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
         <v>66.3</v>
       </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
         <v>33.7</v>
       </c>
-      <c r="E24" t="n">
+      <c r="G24" t="n">
         <v>72.59</v>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t xml:space="preserve">  It's Emily, the greatest girl in the world.  I can't stop thinking about her.</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>milkywayoriginal_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H24" t="n">
+      <c r="J24" t="n">
         <v>0.02515337423312883</v>
       </c>
-      <c r="I24" t="n">
+      <c r="K24" t="n">
         <v>0.03893773796806092</v>
       </c>
-      <c r="J24" t="n">
+      <c r="L24" t="n">
         <v>0.02340182648401826</v>
       </c>
-      <c r="K24" t="n">
+      <c r="M24" t="n">
         <v>0.01794117647058823</v>
       </c>
-      <c r="L24" t="n">
+      <c r="N24" t="n">
         <v>0.05246507100320659</v>
       </c>
-      <c r="M24" t="n">
+      <c r="O24" t="n">
         <v>0.08770639195085944</v>
       </c>
-      <c r="N24" t="n">
+      <c r="P24" t="n">
         <v>0.04989661411217369</v>
       </c>
-      <c r="O24" t="n">
+      <c r="Q24" t="n">
         <v>0.07472565936904083</v>
       </c>
-      <c r="P24" t="n">
+      <c r="R24" t="n">
         <v>0.0861173353250818</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="S24" t="n">
         <v>0.07457010582010581</v>
       </c>
-      <c r="R24" t="n">
+      <c r="T24" t="n">
         <v>2</v>
       </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
         <v>0.112156862745098</v>
       </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" t="n">
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
         <v>0.06428571428571429</v>
       </c>
-      <c r="W24" t="n">
-        <v>0</v>
-      </c>
-      <c r="X24" t="n">
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
         <v>0.03558383409921056</v>
       </c>
-      <c r="Y24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z24" t="n">
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
         <v>0.1608892921960073</v>
       </c>
-      <c r="AA24" t="n">
+      <c r="AC24" t="n">
         <v>0.04827586206896552</v>
       </c>
-      <c r="AB24" t="n">
+      <c r="AD24" t="n">
         <v>0.1489883482916076</v>
       </c>
-      <c r="AC24" t="n">
+      <c r="AE24" t="n">
         <v>0.1461308309533524</v>
       </c>
-      <c r="AD24" t="n">
+      <c r="AF24" t="n">
         <v>0.1393872277593208</v>
       </c>
-      <c r="AE24" t="n">
+      <c r="AG24" t="n">
         <v>0.04088050314465409</v>
       </c>
-      <c r="AF24" t="n">
+      <c r="AH24" t="n">
         <v>0.09156573763315336</v>
       </c>
-      <c r="AG24" t="n">
+      <c r="AI24" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3009,104 +3249,114 @@
       <c r="A25" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="B25" t="n">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>260.788</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>254.674</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
         <v>77.8</v>
       </c>
-      <c r="C25" t="n">
+      <c r="E25" t="n">
         <v>9.4</v>
       </c>
-      <c r="D25" t="n">
+      <c r="F25" t="n">
         <v>12.8</v>
       </c>
-      <c r="E25" t="n">
+      <c r="G25" t="n">
         <v>19.01</v>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t xml:space="preserve">  We were supposed to marry in the spring, but I was afraid to commit.  I'm still obsessed with her.</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>milkywayoriginal_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H25" t="n">
+      <c r="J25" t="n">
         <v>0.05294117647058824</v>
       </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="n">
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
         <v>0.02943969610636277</v>
       </c>
-      <c r="K25" t="n">
+      <c r="M25" t="n">
         <v>0.03333333333333333</v>
       </c>
-      <c r="L25" t="n">
+      <c r="N25" t="n">
         <v>0.04597701149425287</v>
       </c>
-      <c r="M25" t="n">
+      <c r="O25" t="n">
         <v>0.05416666666666667</v>
       </c>
-      <c r="N25" t="n">
+      <c r="P25" t="n">
         <v>0.1314932020628223</v>
       </c>
-      <c r="O25" t="n">
+      <c r="Q25" t="n">
         <v>0.05164319248826291</v>
       </c>
-      <c r="P25" t="n">
+      <c r="R25" t="n">
         <v>0.081445523193096</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="S25" t="n">
         <v>0.09755620723362661</v>
       </c>
-      <c r="R25" t="n">
+      <c r="T25" t="n">
         <v>1</v>
       </c>
-      <c r="S25" t="n">
+      <c r="U25" t="n">
         <v>0.1515151515151515</v>
       </c>
-      <c r="T25" t="n">
+      <c r="V25" t="n">
         <v>0.09593023255813954</v>
       </c>
-      <c r="U25" t="n">
+      <c r="W25" t="n">
         <v>0.1591880341880342</v>
       </c>
-      <c r="V25" t="n">
+      <c r="X25" t="n">
         <v>0.04444444444444445</v>
       </c>
-      <c r="W25" t="n">
+      <c r="Y25" t="n">
         <v>0.1681159420289855</v>
       </c>
-      <c r="X25" t="n">
+      <c r="Z25" t="n">
         <v>0.03508771929824561</v>
       </c>
-      <c r="Y25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z25" t="n">
+      <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="n">
         <v>0.08885116015846066</v>
       </c>
-      <c r="AA25" t="n">
+      <c r="AC25" t="n">
         <v>0.04545454545454545</v>
       </c>
-      <c r="AB25" t="n">
+      <c r="AD25" t="n">
         <v>0.09523809523809523</v>
       </c>
-      <c r="AC25" t="n">
+      <c r="AE25" t="n">
         <v>0.1800213675213675</v>
       </c>
-      <c r="AD25" t="n">
+      <c r="AF25" t="n">
         <v>0.07692307692307693</v>
       </c>
-      <c r="AE25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF25" t="n">
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
         <v>0.1832167832167832</v>
       </c>
-      <c r="AG25" t="n">
+      <c r="AI25" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3114,104 +3364,114 @@
       <c r="A26" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="B26" t="n">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>270.92</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>261.709</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
         <v>82.5</v>
       </c>
-      <c r="C26" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" t="n">
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
         <v>17.5</v>
       </c>
-      <c r="E26" t="n">
+      <c r="G26" t="n">
         <v>64.86</v>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t xml:space="preserve">  I dream about her constantly, and I imagine her face in almost every woman I see.  To be honest, you are the twentieth therapist I've gone to.</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>milkywayoriginal_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H26" t="n">
+      <c r="J26" t="n">
         <v>0.02817553908355795</v>
       </c>
-      <c r="I26" t="n">
+      <c r="K26" t="n">
         <v>0.07490164268472366</v>
       </c>
-      <c r="J26" t="n">
+      <c r="L26" t="n">
         <v>0.05073866247866773</v>
       </c>
-      <c r="K26" t="n">
+      <c r="M26" t="n">
         <v>0.02172949002217295</v>
       </c>
-      <c r="L26" t="n">
+      <c r="N26" t="n">
         <v>0.03399901984807645</v>
       </c>
-      <c r="M26" t="n">
+      <c r="O26" t="n">
         <v>0.08471499925827418</v>
       </c>
-      <c r="N26" t="n">
+      <c r="P26" t="n">
         <v>0.0624201195629767</v>
       </c>
-      <c r="O26" t="n">
+      <c r="Q26" t="n">
         <v>0.04538829948666014</v>
       </c>
-      <c r="P26" t="n">
+      <c r="R26" t="n">
         <v>0.07593763399289132</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="S26" t="n">
         <v>0.06866806390177811</v>
       </c>
-      <c r="R26" t="n">
+      <c r="T26" t="n">
         <v>7</v>
       </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
         <v>0.06164383561643835</v>
       </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
       <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
         <v>0.1320493066255778</v>
       </c>
-      <c r="X26" t="n">
+      <c r="Z26" t="n">
         <v>0.1164855072463768</v>
       </c>
-      <c r="Y26" t="n">
+      <c r="AA26" t="n">
         <v>0.02164502164502164</v>
       </c>
-      <c r="Z26" t="n">
+      <c r="AB26" t="n">
         <v>0.2567096081588836</v>
       </c>
-      <c r="AA26" t="n">
+      <c r="AC26" t="n">
         <v>0.08866180048661799</v>
       </c>
-      <c r="AB26" t="n">
+      <c r="AD26" t="n">
         <v>0.1741663113006397</v>
       </c>
-      <c r="AC26" t="n">
+      <c r="AE26" t="n">
         <v>0.1534755372932906</v>
       </c>
-      <c r="AD26" t="n">
+      <c r="AF26" t="n">
         <v>0.06024096385542169</v>
       </c>
-      <c r="AE26" t="n">
+      <c r="AG26" t="n">
         <v>0.04519774011299435</v>
       </c>
-      <c r="AF26" t="n">
+      <c r="AH26" t="n">
         <v>0.0731829573934837</v>
       </c>
-      <c r="AG26" t="n">
+      <c r="AI26" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -3219,104 +3479,114 @@
       <c r="A27" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="B27" t="n">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>283.635</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>272.281</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
         <v>87.09999999999999</v>
       </c>
-      <c r="C27" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" t="n">
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
         <v>12.9</v>
       </c>
-      <c r="E27" t="n">
+      <c r="G27" t="n">
         <v>51.13</v>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t xml:space="preserve">  Do you like chocolate, Mr. Smith?  Thomas didn't understand the relevance of the question, but he replied nevertheless, I'm not crazy about it, but I take a bite now and then.</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>milkywayoriginal_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H27" t="n">
+      <c r="J27" t="n">
         <v>0.02209877211013144</v>
       </c>
-      <c r="I27" t="n">
+      <c r="K27" t="n">
         <v>0.001583873290136789</v>
       </c>
-      <c r="J27" t="n">
+      <c r="L27" t="n">
         <v>0.03046013148228499</v>
       </c>
-      <c r="K27" t="n">
+      <c r="M27" t="n">
         <v>0.03890260544968958</v>
       </c>
-      <c r="L27" t="n">
+      <c r="N27" t="n">
         <v>0.04659104850492411</v>
       </c>
-      <c r="M27" t="n">
+      <c r="O27" t="n">
         <v>0.05875735912531539</v>
       </c>
-      <c r="N27" t="n">
+      <c r="P27" t="n">
         <v>0.0856930316953161</v>
       </c>
-      <c r="O27" t="n">
+      <c r="Q27" t="n">
         <v>0.0298989898989899</v>
       </c>
-      <c r="P27" t="n">
+      <c r="R27" t="n">
         <v>0.006896551724137929</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="S27" t="n">
         <v>0.03870967741935484</v>
       </c>
-      <c r="R27" t="n">
+      <c r="T27" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="S27" t="n">
+      <c r="U27" t="n">
         <v>0.03325842162213582</v>
       </c>
-      <c r="T27" t="n">
+      <c r="V27" t="n">
         <v>0.03259505352528608</v>
       </c>
-      <c r="U27" t="n">
+      <c r="W27" t="n">
         <v>0.03447472629862567</v>
       </c>
-      <c r="V27" t="n">
+      <c r="X27" t="n">
         <v>0.02874018553684537</v>
       </c>
-      <c r="W27" t="n">
+      <c r="Y27" t="n">
         <v>0.06463467358408992</v>
       </c>
-      <c r="X27" t="n">
+      <c r="Z27" t="n">
         <v>0.006561679790026247</v>
       </c>
-      <c r="Y27" t="n">
+      <c r="AA27" t="n">
         <v>0.03180354267310789</v>
       </c>
-      <c r="Z27" t="n">
+      <c r="AB27" t="n">
         <v>0.02347417840375587</v>
       </c>
-      <c r="AA27" t="n">
+      <c r="AC27" t="n">
         <v>0.02150537634408602</v>
       </c>
-      <c r="AB27" t="n">
+      <c r="AD27" t="n">
         <v>0.03888888888888889</v>
       </c>
-      <c r="AC27" t="n">
+      <c r="AE27" t="n">
         <v>0.04301075268817204</v>
       </c>
-      <c r="AD27" t="n">
+      <c r="AF27" t="n">
         <v>0.03300330033003301</v>
       </c>
-      <c r="AE27" t="n">
+      <c r="AG27" t="n">
         <v>0.0430172068827531</v>
       </c>
-      <c r="AF27" t="n">
+      <c r="AH27" t="n">
         <v>0.03787878787878788</v>
       </c>
-      <c r="AG27" t="n">
+      <c r="AI27" t="n">
         <v>0.375</v>
       </c>
     </row>
@@ -3324,104 +3594,114 @@
       <c r="A28" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="B28" t="n">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>292.232</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>284.138</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
         <v>89.3</v>
       </c>
-      <c r="C28" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" t="n">
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
         <v>10.7</v>
       </c>
-      <c r="E28" t="n">
+      <c r="G28" t="n">
         <v>45.88</v>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t xml:space="preserve"> Just keep your eyes on the Milky Way, Andre said, as he started to gently dangle a miniature Milky Way which was tied to a string.</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>milkywayoriginal_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
         <v>0.01550387596899225</v>
       </c>
-      <c r="J28" t="n">
+      <c r="L28" t="n">
         <v>0.01496821479320918</v>
       </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
       <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
         <v>0.09340247145853513</v>
       </c>
-      <c r="N28" t="n">
+      <c r="P28" t="n">
         <v>0.07579641411410599</v>
       </c>
-      <c r="O28" t="n">
+      <c r="Q28" t="n">
         <v>0.05160006497725796</v>
       </c>
-      <c r="P28" t="n">
+      <c r="R28" t="n">
         <v>0.0759762229280649</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="S28" t="n">
         <v>0.09268066110253759</v>
       </c>
-      <c r="R28" t="n">
+      <c r="T28" t="n">
         <v>0.8571428571428571</v>
       </c>
-      <c r="S28" t="n">
+      <c r="U28" t="n">
         <v>0.06052631578947369</v>
       </c>
-      <c r="T28" t="n">
+      <c r="V28" t="n">
         <v>0.1341949860724234</v>
       </c>
-      <c r="U28" t="n">
+      <c r="W28" t="n">
         <v>0.06779661016949153</v>
       </c>
-      <c r="V28" t="n">
+      <c r="X28" t="n">
         <v>0.04856230031948881</v>
       </c>
-      <c r="W28" t="n">
+      <c r="Y28" t="n">
         <v>0.06357615894039735</v>
       </c>
-      <c r="X28" t="n">
+      <c r="Z28" t="n">
         <v>0.07315175097276264</v>
       </c>
-      <c r="Y28" t="n">
+      <c r="AA28" t="n">
         <v>0.01379310344827586</v>
       </c>
-      <c r="Z28" t="n">
+      <c r="AB28" t="n">
         <v>0.06491342809801474</v>
       </c>
-      <c r="AA28" t="n">
+      <c r="AC28" t="n">
         <v>0.01585288522511097</v>
       </c>
-      <c r="AB28" t="n">
+      <c r="AD28" t="n">
         <v>0.03710817145966978</v>
       </c>
-      <c r="AC28" t="n">
+      <c r="AE28" t="n">
         <v>0.03040322159846041</v>
       </c>
-      <c r="AD28" t="n">
+      <c r="AF28" t="n">
         <v>0.08199079310873794</v>
       </c>
-      <c r="AE28" t="n">
+      <c r="AG28" t="n">
         <v>0.03560854289210848</v>
       </c>
-      <c r="AF28" t="n">
+      <c r="AH28" t="n">
         <v>0.08464384464259349</v>
       </c>
-      <c r="AG28" t="n">
+      <c r="AI28" t="n">
         <v>0.625</v>
       </c>
     </row>
@@ -3429,104 +3709,114 @@
       <c r="A29" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="B29" t="n">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>302.43</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>293.555</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
         <v>74.2</v>
       </c>
-      <c r="C29" t="n">
+      <c r="E29" t="n">
         <v>7.8</v>
       </c>
-      <c r="D29" t="n">
+      <c r="F29" t="n">
         <v>18</v>
       </c>
-      <c r="E29" t="n">
+      <c r="G29" t="n">
         <v>44.04</v>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t xml:space="preserve">  Aren't you supposed to do that with a silver watch?  Thomas said doubtfully.  Put your trust in Andre, and everything will be just fine.</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>milkywayoriginal_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H29" t="n">
+      <c r="J29" t="n">
         <v>0.07734724292101341</v>
       </c>
-      <c r="I29" t="n">
+      <c r="K29" t="n">
         <v>0.03670145477545857</v>
       </c>
-      <c r="J29" t="n">
+      <c r="L29" t="n">
         <v>0.07318950167699326</v>
       </c>
-      <c r="K29" t="n">
+      <c r="M29" t="n">
         <v>0.05152671755725191</v>
       </c>
-      <c r="L29" t="n">
+      <c r="N29" t="n">
         <v>0.03539823008849557</v>
       </c>
-      <c r="M29" t="n">
+      <c r="O29" t="n">
         <v>0.01105554886130859</v>
       </c>
-      <c r="N29" t="n">
+      <c r="P29" t="n">
         <v>0.04030322477599527</v>
       </c>
-      <c r="O29" t="n">
+      <c r="Q29" t="n">
         <v>0.01652892561983471</v>
       </c>
-      <c r="P29" t="n">
+      <c r="R29" t="n">
         <v>0.05213023294332857</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="S29" t="n">
         <v>0.06927490993581094</v>
       </c>
-      <c r="R29" t="n">
+      <c r="T29" t="n">
         <v>0.8</v>
       </c>
-      <c r="S29" t="n">
+      <c r="U29" t="n">
         <v>0.0564516129032258</v>
       </c>
-      <c r="T29" t="n">
+      <c r="V29" t="n">
         <v>0.1673002385211688</v>
       </c>
-      <c r="U29" t="n">
+      <c r="W29" t="n">
         <v>0.1762370019397717</v>
       </c>
-      <c r="V29" t="n">
+      <c r="X29" t="n">
         <v>0.01388888888888889</v>
       </c>
-      <c r="W29" t="n">
+      <c r="Y29" t="n">
         <v>0.1480106100795756</v>
       </c>
-      <c r="X29" t="n">
+      <c r="Z29" t="n">
         <v>0.08881578947368421</v>
       </c>
-      <c r="Y29" t="n">
+      <c r="AA29" t="n">
         <v>0.04487179487179487</v>
       </c>
-      <c r="Z29" t="n">
+      <c r="AB29" t="n">
         <v>0.05803375230728663</v>
       </c>
-      <c r="AA29" t="n">
+      <c r="AC29" t="n">
         <v>0.01981610653138871</v>
       </c>
-      <c r="AB29" t="n">
+      <c r="AD29" t="n">
         <v>0.02169385629989587</v>
       </c>
-      <c r="AC29" t="n">
+      <c r="AE29" t="n">
         <v>0.07721132240291143</v>
       </c>
-      <c r="AD29" t="n">
+      <c r="AF29" t="n">
         <v>0.0166848023213638</v>
       </c>
-      <c r="AE29" t="n">
+      <c r="AG29" t="n">
         <v>0.03154590366405928</v>
       </c>
-      <c r="AF29" t="n">
+      <c r="AH29" t="n">
         <v>0.0776365852208549</v>
       </c>
-      <c r="AG29" t="n">
+      <c r="AI29" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -3534,104 +3824,114 @@
       <c r="A30" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="B30" t="n">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>313.205</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>303.492</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
         <v>71.3</v>
       </c>
-      <c r="C30" t="n">
+      <c r="E30" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="D30" t="n">
+      <c r="F30" t="n">
         <v>20.4</v>
       </c>
-      <c r="E30" t="n">
+      <c r="G30" t="n">
         <v>50.06</v>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t xml:space="preserve">  He took a deep breath and tried not to laugh.  The next thing he remembered was waking up and feeling like he could really use a good chiropractic therapy.</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>milkywayoriginal_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H30" t="n">
+      <c r="J30" t="n">
         <v>0.0150841372072629</v>
       </c>
-      <c r="I30" t="n">
+      <c r="K30" t="n">
         <v>0.02578700387545407</v>
       </c>
-      <c r="J30" t="n">
+      <c r="L30" t="n">
         <v>0.05693707669485611</v>
       </c>
-      <c r="K30" t="n">
+      <c r="M30" t="n">
         <v>0.04292611950314048</v>
       </c>
-      <c r="L30" t="n">
+      <c r="N30" t="n">
         <v>0.03153832034320263</v>
       </c>
-      <c r="M30" t="n">
+      <c r="O30" t="n">
         <v>0.09925729507978831</v>
       </c>
-      <c r="N30" t="n">
+      <c r="P30" t="n">
         <v>0.07056246342357581</v>
       </c>
-      <c r="O30" t="n">
+      <c r="Q30" t="n">
         <v>0.04436216487413296</v>
       </c>
-      <c r="P30" t="n">
+      <c r="R30" t="n">
         <v>0.04734268303152264</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="S30" t="n">
         <v>0.04541302224776045</v>
       </c>
-      <c r="R30" t="n">
+      <c r="T30" t="n">
         <v>1.333333333333333</v>
       </c>
-      <c r="S30" t="n">
+      <c r="U30" t="n">
         <v>0.06565028407877313</v>
       </c>
-      <c r="T30" t="n">
+      <c r="V30" t="n">
         <v>0.05842601018932109</v>
       </c>
-      <c r="U30" t="n">
+      <c r="W30" t="n">
         <v>0.03551681018786282</v>
       </c>
-      <c r="V30" t="n">
+      <c r="X30" t="n">
         <v>0.03512212279641509</v>
       </c>
-      <c r="W30" t="n">
+      <c r="Y30" t="n">
         <v>0.09982349050008905</v>
       </c>
-      <c r="X30" t="n">
+      <c r="Z30" t="n">
         <v>0.05090791826921045</v>
       </c>
-      <c r="Y30" t="n">
+      <c r="AA30" t="n">
         <v>0.03902061277553853</v>
       </c>
-      <c r="Z30" t="n">
+      <c r="AB30" t="n">
         <v>0.1092022310019298</v>
       </c>
-      <c r="AA30" t="n">
+      <c r="AC30" t="n">
         <v>0.09684711026012589</v>
       </c>
-      <c r="AB30" t="n">
+      <c r="AD30" t="n">
         <v>0.114186770251238</v>
       </c>
-      <c r="AC30" t="n">
+      <c r="AE30" t="n">
         <v>0.09642840780422673</v>
       </c>
-      <c r="AD30" t="n">
+      <c r="AF30" t="n">
         <v>0.03195684523809524</v>
       </c>
-      <c r="AE30" t="n">
+      <c r="AG30" t="n">
         <v>0.06384217210591132</v>
       </c>
-      <c r="AF30" t="n">
+      <c r="AH30" t="n">
         <v>0.0709451060783548</v>
       </c>
-      <c r="AG30" t="n">
+      <c r="AI30" t="n">
         <v>1.333333333333333</v>
       </c>
     </row>
@@ -3639,104 +3939,114 @@
       <c r="A31" s="1" t="n">
         <v>29</v>
       </c>
-      <c r="B31" t="n">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>320.534</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>313.905</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
         <v>66.2</v>
       </c>
-      <c r="C31" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" t="n">
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
         <v>33.8</v>
       </c>
-      <c r="E31" t="n">
+      <c r="G31" t="n">
         <v>84.81</v>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t xml:space="preserve">  When he left Andre's clinic an hour later, he felt better than he had for ages.  It was like a miracle.</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>milkywayoriginal_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H31" t="n">
+      <c r="J31" t="n">
         <v>0.001954887218045113</v>
       </c>
-      <c r="I31" t="n">
+      <c r="K31" t="n">
         <v>0.0382731643911926</v>
       </c>
-      <c r="J31" t="n">
+      <c r="L31" t="n">
         <v>0.002966958867161159</v>
       </c>
-      <c r="K31" t="n">
+      <c r="M31" t="n">
         <v>0.001299638989169675</v>
       </c>
-      <c r="L31" t="n">
+      <c r="N31" t="n">
         <v>0.00242914979757085</v>
       </c>
-      <c r="M31" t="n">
+      <c r="O31" t="n">
         <v>0.07266921933968887</v>
       </c>
-      <c r="N31" t="n">
+      <c r="P31" t="n">
         <v>0.03187691927206777</v>
       </c>
-      <c r="O31" t="n">
+      <c r="Q31" t="n">
         <v>0.06185324736043304</v>
       </c>
-      <c r="P31" t="n">
+      <c r="R31" t="n">
         <v>0.04474986178706348</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="S31" t="n">
         <v>0.05196217866183417</v>
       </c>
-      <c r="R31" t="n">
+      <c r="T31" t="n">
         <v>1</v>
       </c>
-      <c r="S31" t="n">
+      <c r="U31" t="n">
         <v>0.08982027050553851</v>
       </c>
-      <c r="T31" t="n">
+      <c r="V31" t="n">
         <v>0.04988855713024097</v>
       </c>
-      <c r="U31" t="n">
+      <c r="W31" t="n">
         <v>0.03272468272468272</v>
       </c>
-      <c r="V31" t="n">
+      <c r="X31" t="n">
         <v>0.04555547119773767</v>
       </c>
-      <c r="W31" t="n">
+      <c r="Y31" t="n">
         <v>0.02026228563193544</v>
       </c>
-      <c r="X31" t="n">
+      <c r="Z31" t="n">
         <v>0.05876218269919058</v>
       </c>
-      <c r="Y31" t="n">
+      <c r="AA31" t="n">
         <v>0.005986887508626639</v>
       </c>
-      <c r="Z31" t="n">
+      <c r="AB31" t="n">
         <v>0.07093596059113301</v>
       </c>
-      <c r="AA31" t="n">
+      <c r="AC31" t="n">
         <v>0.06139901963806764</v>
       </c>
-      <c r="AB31" t="n">
+      <c r="AD31" t="n">
         <v>0.03724137931034483</v>
       </c>
-      <c r="AC31" t="n">
+      <c r="AE31" t="n">
         <v>0.04050632911392405</v>
       </c>
-      <c r="AD31" t="n">
+      <c r="AF31" t="n">
         <v>0.1031569537262453</v>
       </c>
-      <c r="AE31" t="n">
+      <c r="AG31" t="n">
         <v>0.01166666666666667</v>
       </c>
-      <c r="AF31" t="n">
+      <c r="AH31" t="n">
         <v>0.03845645248542405</v>
       </c>
-      <c r="AG31" t="n">
+      <c r="AI31" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3744,104 +4054,114 @@
       <c r="A32" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="B32" t="n">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>330.547</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>321.355</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
         <v>62.7</v>
       </c>
-      <c r="C32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" t="n">
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
         <v>37.3</v>
       </c>
-      <c r="E32" t="n">
+      <c r="G32" t="n">
         <v>92.86999999999999</v>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t xml:space="preserve">  His back felt great, and he had new hope in his heart.  As he strolled down the street, he spotted a girl that looked exactly like Emily.</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>milkywayoriginal_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H32" t="n">
+      <c r="J32" t="n">
         <v>0.02770015306922404</v>
       </c>
-      <c r="I32" t="n">
+      <c r="K32" t="n">
         <v>0.03740491683429128</v>
       </c>
-      <c r="J32" t="n">
+      <c r="L32" t="n">
         <v>0.04084021616180632</v>
       </c>
-      <c r="K32" t="n">
+      <c r="M32" t="n">
         <v>0.03574339906365502</v>
       </c>
-      <c r="L32" t="n">
+      <c r="N32" t="n">
         <v>0.04775391327568897</v>
       </c>
-      <c r="M32" t="n">
+      <c r="O32" t="n">
         <v>0.04933947817339689</v>
       </c>
-      <c r="N32" t="n">
+      <c r="P32" t="n">
         <v>0.01652338684904453</v>
       </c>
-      <c r="O32" t="n">
+      <c r="Q32" t="n">
         <v>0.0329147684473653</v>
       </c>
-      <c r="P32" t="n">
+      <c r="R32" t="n">
         <v>0.0214097282648628</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="S32" t="n">
         <v>0.02578982374459594</v>
       </c>
-      <c r="R32" t="n">
+      <c r="T32" t="n">
         <v>3.333333333333333</v>
       </c>
-      <c r="S32" t="n">
+      <c r="U32" t="n">
         <v>0.07451823169335377</v>
       </c>
-      <c r="T32" t="n">
+      <c r="V32" t="n">
         <v>0.1065141341834367</v>
       </c>
-      <c r="U32" t="n">
+      <c r="W32" t="n">
         <v>0.06835801950633648</v>
       </c>
-      <c r="V32" t="n">
+      <c r="X32" t="n">
         <v>0.04441282126327063</v>
       </c>
-      <c r="W32" t="n">
+      <c r="Y32" t="n">
         <v>0.04116704823366377</v>
       </c>
-      <c r="X32" t="n">
+      <c r="Z32" t="n">
         <v>0.04790283831527547</v>
       </c>
-      <c r="Y32" t="n">
+      <c r="AA32" t="n">
         <v>0.01561321273886866</v>
       </c>
-      <c r="Z32" t="n">
+      <c r="AB32" t="n">
         <v>0.04128475832629178</v>
       </c>
-      <c r="AA32" t="n">
+      <c r="AC32" t="n">
         <v>0.02365149303996408</v>
       </c>
-      <c r="AB32" t="n">
+      <c r="AD32" t="n">
         <v>0.02343644354293441</v>
       </c>
-      <c r="AC32" t="n">
+      <c r="AE32" t="n">
         <v>0.04975254592176644</v>
       </c>
-      <c r="AD32" t="n">
+      <c r="AF32" t="n">
         <v>0.07260263321584076</v>
       </c>
-      <c r="AE32" t="n">
+      <c r="AG32" t="n">
         <v>0.02797368166073202</v>
       </c>
-      <c r="AF32" t="n">
+      <c r="AH32" t="n">
         <v>0.02632692574009566</v>
       </c>
-      <c r="AG32" t="n">
+      <c r="AI32" t="n">
         <v>1.6</v>
       </c>
     </row>
@@ -3849,104 +4169,114 @@
       <c r="A33" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="B33" t="n">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>341.104</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>331.248</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
         <v>63.2</v>
       </c>
-      <c r="C33" t="n">
+      <c r="E33" t="n">
         <v>7.399999999999999</v>
       </c>
-      <c r="D33" t="n">
+      <c r="F33" t="n">
         <v>29.4</v>
       </c>
-      <c r="E33" t="n">
+      <c r="G33" t="n">
         <v>78.75999999999999</v>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t xml:space="preserve">  But after another second, he realized that he was imagining.  Feeling better, he stopped to buy a Milky Way and continued walking home lighthearted.</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>milkywayoriginal_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H33" t="n">
+      <c r="J33" t="n">
         <v>0.01769911504424779</v>
       </c>
-      <c r="I33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" t="n">
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
         <v>0.01588983050847458</v>
       </c>
-      <c r="K33" t="n">
+      <c r="M33" t="n">
         <v>0.01834914182475158</v>
       </c>
-      <c r="L33" t="n">
+      <c r="N33" t="n">
         <v>0.04259004994299111</v>
       </c>
-      <c r="M33" t="n">
+      <c r="O33" t="n">
         <v>0.1008592964372398</v>
       </c>
-      <c r="N33" t="n">
+      <c r="P33" t="n">
         <v>0.09721610173230073</v>
       </c>
-      <c r="O33" t="n">
+      <c r="Q33" t="n">
         <v>0.07491837664344547</v>
       </c>
-      <c r="P33" t="n">
+      <c r="R33" t="n">
         <v>0.06172644635449169</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="S33" t="n">
         <v>0.04464021430708513</v>
       </c>
-      <c r="R33" t="n">
+      <c r="T33" t="n">
         <v>2</v>
       </c>
-      <c r="S33" t="n">
+      <c r="U33" t="n">
         <v>0.1238829547186705</v>
       </c>
-      <c r="T33" t="n">
+      <c r="V33" t="n">
         <v>0.05599688205692538</v>
       </c>
-      <c r="U33" t="n">
+      <c r="W33" t="n">
         <v>0.07646851292232977</v>
       </c>
-      <c r="V33" t="n">
+      <c r="X33" t="n">
         <v>0.06925389964292426</v>
       </c>
-      <c r="W33" t="n">
+      <c r="Y33" t="n">
         <v>0.1204328076409807</v>
       </c>
-      <c r="X33" t="n">
+      <c r="Z33" t="n">
         <v>0.1050903097794129</v>
       </c>
-      <c r="Y33" t="n">
+      <c r="AA33" t="n">
         <v>0.08574929971988797</v>
       </c>
-      <c r="Z33" t="n">
+      <c r="AB33" t="n">
         <v>0.1324766653880578</v>
       </c>
-      <c r="AA33" t="n">
+      <c r="AC33" t="n">
         <v>0.1036813382755006</v>
       </c>
-      <c r="AB33" t="n">
+      <c r="AD33" t="n">
         <v>0.06597701149425288</v>
       </c>
-      <c r="AC33" t="n">
+      <c r="AE33" t="n">
         <v>0.099908100393439</v>
       </c>
-      <c r="AD33" t="n">
+      <c r="AF33" t="n">
         <v>0.05265339966832503</v>
       </c>
-      <c r="AE33" t="n">
+      <c r="AG33" t="n">
         <v>0.05416666666666667</v>
       </c>
-      <c r="AF33" t="n">
+      <c r="AH33" t="n">
         <v>0.07633213888410562</v>
       </c>
-      <c r="AG33" t="n">
+      <c r="AI33" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3954,104 +4284,114 @@
       <c r="A34" s="1" t="n">
         <v>32</v>
       </c>
-      <c r="B34" t="n">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>348.994</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>341.124</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
         <v>89.40000000000001</v>
       </c>
-      <c r="C34" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" t="n">
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
         <v>10.6</v>
       </c>
-      <c r="E34" t="n">
+      <c r="G34" t="n">
         <v>36.12</v>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t xml:space="preserve">  As days went by, he noticed that he was dreaming about Emily less than ever.  He was finally ready to meet her.</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>milkywayoriginal_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H34" t="n">
+      <c r="J34" t="n">
         <v>0.07880539547272973</v>
       </c>
-      <c r="I34" t="n">
+      <c r="K34" t="n">
         <v>0.1077758713408115</v>
       </c>
-      <c r="J34" t="n">
+      <c r="L34" t="n">
         <v>0.05197401935812532</v>
       </c>
-      <c r="K34" t="n">
+      <c r="M34" t="n">
         <v>0.03571428571428571</v>
       </c>
-      <c r="L34" t="n">
+      <c r="N34" t="n">
         <v>0.02911840411840411</v>
       </c>
-      <c r="M34" t="n">
+      <c r="O34" t="n">
         <v>0.01982758620689655</v>
       </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
         <v>0.01865671641791044</v>
       </c>
-      <c r="P34" t="n">
+      <c r="R34" t="n">
         <v>0.04776727819966063</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="S34" t="n">
         <v>0.02224824355971897</v>
       </c>
-      <c r="R34" t="n">
+      <c r="T34" t="n">
         <v>1</v>
       </c>
-      <c r="S34" t="n">
+      <c r="U34" t="n">
         <v>0.1614583333333333</v>
       </c>
-      <c r="T34" t="n">
+      <c r="V34" t="n">
         <v>0.06547619047619048</v>
       </c>
-      <c r="U34" t="n">
+      <c r="W34" t="n">
         <v>0.03888888888888889</v>
       </c>
-      <c r="V34" t="n">
+      <c r="X34" t="n">
         <v>0.1611183480484392</v>
       </c>
-      <c r="W34" t="n">
+      <c r="Y34" t="n">
         <v>0.1216216216216216</v>
       </c>
-      <c r="X34" t="n">
+      <c r="Z34" t="n">
         <v>0.14408633372048</v>
       </c>
-      <c r="Y34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z34" t="n">
+      <c r="AA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" t="n">
         <v>0.02916666666666667</v>
       </c>
-      <c r="AA34" t="n">
+      <c r="AC34" t="n">
         <v>0.1073013024262196</v>
       </c>
-      <c r="AB34" t="n">
+      <c r="AD34" t="n">
         <v>0.08982683982683982</v>
       </c>
-      <c r="AC34" t="n">
+      <c r="AE34" t="n">
         <v>0.03636363636363636</v>
       </c>
-      <c r="AD34" t="n">
+      <c r="AF34" t="n">
         <v>0.08493589743589744</v>
       </c>
-      <c r="AE34" t="n">
+      <c r="AG34" t="n">
         <v>0.02941176470588235</v>
       </c>
-      <c r="AF34" t="n">
+      <c r="AH34" t="n">
         <v>0.0902330417499759</v>
       </c>
-      <c r="AG34" t="n">
+      <c r="AI34" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4059,104 +4399,114 @@
       <c r="A35" s="1" t="n">
         <v>33</v>
       </c>
-      <c r="B35" t="n">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>359.708</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>350.837</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
         <v>100</v>
       </c>
-      <c r="C35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" t="n">
-        <v>0</v>
-      </c>
       <c r="E35" t="n">
         <v>0</v>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="inlineStr">
         <is>
           <t xml:space="preserve">  He called his ex and eventually persuaded her to meet with him at a bar the next day.  When he arrived at the bar, Emily was looking at her watch.</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>milkywayoriginal_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H35" t="n">
+      <c r="J35" t="n">
         <v>0.07222890896709508</v>
       </c>
-      <c r="I35" t="n">
+      <c r="K35" t="n">
         <v>0.0476923956740413</v>
       </c>
-      <c r="J35" t="n">
+      <c r="L35" t="n">
         <v>0.03240614390599813</v>
       </c>
-      <c r="K35" t="n">
+      <c r="M35" t="n">
         <v>0.04601718363186253</v>
       </c>
-      <c r="L35" t="n">
+      <c r="N35" t="n">
         <v>0.042038311603529</v>
       </c>
-      <c r="M35" t="n">
+      <c r="O35" t="n">
         <v>0.01758265287362507</v>
       </c>
-      <c r="N35" t="n">
+      <c r="P35" t="n">
         <v>0.01641121716729261</v>
       </c>
-      <c r="O35" t="n">
+      <c r="Q35" t="n">
         <v>0.03137878839293886</v>
       </c>
-      <c r="P35" t="n">
+      <c r="R35" t="n">
         <v>0.04586180488203225</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="S35" t="n">
         <v>0.0283702522967759</v>
       </c>
-      <c r="R35" t="n">
+      <c r="T35" t="n">
         <v>3</v>
       </c>
-      <c r="S35" t="n">
+      <c r="U35" t="n">
         <v>0.06640211640211641</v>
       </c>
-      <c r="T35" t="n">
+      <c r="V35" t="n">
         <v>0.03256410256410256</v>
       </c>
-      <c r="U35" t="n">
+      <c r="W35" t="n">
         <v>0.03933607673710893</v>
       </c>
-      <c r="V35" t="n">
+      <c r="X35" t="n">
         <v>0.0437610229276896</v>
       </c>
-      <c r="W35" t="n">
+      <c r="Y35" t="n">
         <v>0.06527169345715589</v>
       </c>
-      <c r="X35" t="n">
+      <c r="Z35" t="n">
         <v>0.03209876543209876</v>
       </c>
-      <c r="Y35" t="n">
+      <c r="AA35" t="n">
         <v>0.03637838344562236</v>
       </c>
-      <c r="Z35" t="n">
+      <c r="AB35" t="n">
         <v>0.05045716398927409</v>
       </c>
-      <c r="AA35" t="n">
+      <c r="AC35" t="n">
         <v>0.0903900704083514</v>
       </c>
-      <c r="AB35" t="n">
+      <c r="AD35" t="n">
         <v>0.08730368822322845</v>
       </c>
-      <c r="AC35" t="n">
+      <c r="AE35" t="n">
         <v>0.0704536192881936</v>
       </c>
-      <c r="AD35" t="n">
+      <c r="AF35" t="n">
         <v>0.05297689464803199</v>
       </c>
-      <c r="AE35" t="n">
+      <c r="AG35" t="n">
         <v>0.06449793860961374</v>
       </c>
-      <c r="AF35" t="n">
+      <c r="AH35" t="n">
         <v>0.05378342563713165</v>
       </c>
-      <c r="AG35" t="n">
+      <c r="AI35" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4164,104 +4514,114 @@
       <c r="A36" s="1" t="n">
         <v>34</v>
       </c>
-      <c r="B36" t="n">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>368.07</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>360.903</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
         <v>78</v>
       </c>
-      <c r="C36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" t="n">
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
         <v>22</v>
       </c>
-      <c r="E36" t="n">
+      <c r="G36" t="n">
         <v>62.29</v>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t xml:space="preserve">  How are you doing, Emily?  he asked, not losing control of his body for a change.  I have been better.</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>milkywayoriginal_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H36" t="n">
+      <c r="J36" t="n">
         <v>0.02243346007604563</v>
       </c>
-      <c r="I36" t="n">
+      <c r="K36" t="n">
         <v>0.0240859883653735</v>
       </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="n">
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
         <v>0.03494433529796988</v>
       </c>
-      <c r="L36" t="n">
+      <c r="N36" t="n">
         <v>0.01935483870967742</v>
       </c>
-      <c r="M36" t="n">
+      <c r="O36" t="n">
         <v>0.08710591684688895</v>
       </c>
-      <c r="N36" t="n">
+      <c r="P36" t="n">
         <v>0.06641249006140601</v>
       </c>
-      <c r="O36" t="n">
+      <c r="Q36" t="n">
         <v>0.08904940372445461</v>
       </c>
-      <c r="P36" t="n">
+      <c r="R36" t="n">
         <v>0.07446173593780718</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="S36" t="n">
         <v>0.08654193665551749</v>
       </c>
-      <c r="R36" t="n">
+      <c r="T36" t="n">
         <v>2.5</v>
       </c>
-      <c r="S36" t="n">
+      <c r="U36" t="n">
         <v>0.05932629462041226</v>
       </c>
-      <c r="T36" t="n">
+      <c r="V36" t="n">
         <v>0.04573849878934625</v>
       </c>
-      <c r="U36" t="n">
+      <c r="W36" t="n">
         <v>0.02790697674418605</v>
       </c>
-      <c r="V36" t="n">
+      <c r="X36" t="n">
         <v>0.04299736004873757</v>
       </c>
-      <c r="W36" t="n">
-        <v>0</v>
-      </c>
-      <c r="X36" t="n">
+      <c r="Y36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="n">
         <v>0.1388050360281241</v>
       </c>
-      <c r="Y36" t="n">
+      <c r="AA36" t="n">
         <v>0.02553191489361702</v>
       </c>
-      <c r="Z36" t="n">
+      <c r="AB36" t="n">
         <v>0.1573437657153361</v>
       </c>
-      <c r="AA36" t="n">
+      <c r="AC36" t="n">
         <v>0.1088332932738363</v>
       </c>
-      <c r="AB36" t="n">
+      <c r="AD36" t="n">
         <v>0.08894647408666101</v>
       </c>
-      <c r="AC36" t="n">
+      <c r="AE36" t="n">
         <v>0.05429052429052429</v>
       </c>
-      <c r="AD36" t="n">
+      <c r="AF36" t="n">
         <v>0.1560563567312034</v>
       </c>
-      <c r="AE36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF36" t="n">
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
         <v>0.09812630303265965</v>
       </c>
-      <c r="AG36" t="n">
+      <c r="AI36" t="n">
         <v>2.5</v>
       </c>
     </row>
@@ -4269,104 +4629,114 @@
       <c r="A37" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="B37" t="n">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>374.636</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>368.45</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
         <v>85.39999999999999</v>
       </c>
-      <c r="C37" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" t="n">
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
         <v>14.6</v>
       </c>
-      <c r="E37" t="n">
+      <c r="G37" t="n">
         <v>44.04</v>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t xml:space="preserve">  How are you these days?  Getting better, he answered, actually believing in the words that he was saying.</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>milkywayoriginal_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H37" t="n">
+      <c r="J37" t="n">
         <v>0.08236314897398493</v>
       </c>
-      <c r="I37" t="n">
+      <c r="K37" t="n">
         <v>0.04386446886446887</v>
       </c>
-      <c r="J37" t="n">
+      <c r="L37" t="n">
         <v>0.04380440241044526</v>
       </c>
-      <c r="K37" t="n">
+      <c r="M37" t="n">
         <v>0.0664801340723427</v>
       </c>
-      <c r="L37" t="n">
+      <c r="N37" t="n">
         <v>0.03212290502793296</v>
       </c>
-      <c r="M37" t="n">
+      <c r="O37" t="n">
         <v>0.01538461538461538</v>
       </c>
-      <c r="N37" t="n">
+      <c r="P37" t="n">
         <v>0.0494005994005994</v>
       </c>
-      <c r="O37" t="n">
+      <c r="Q37" t="n">
         <v>0.03301492537313433</v>
       </c>
-      <c r="P37" t="n">
+      <c r="R37" t="n">
         <v>0.01770833333333333</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="S37" t="n">
         <v>0.06989687804364421</v>
       </c>
-      <c r="R37" t="n">
+      <c r="T37" t="n">
         <v>1</v>
       </c>
-      <c r="S37" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" t="n">
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
         <v>0.02966101694915254</v>
       </c>
-      <c r="U37" t="n">
+      <c r="W37" t="n">
         <v>0.04651162790697674</v>
       </c>
-      <c r="V37" t="n">
+      <c r="X37" t="n">
         <v>0.02298850574712644</v>
       </c>
-      <c r="W37" t="n">
+      <c r="Y37" t="n">
         <v>0.09527576853526221</v>
       </c>
-      <c r="X37" t="n">
+      <c r="Z37" t="n">
         <v>0.05803622136682022</v>
       </c>
-      <c r="Y37" t="n">
+      <c r="AA37" t="n">
         <v>0.07255877034358046</v>
       </c>
-      <c r="Z37" t="n">
+      <c r="AB37" t="n">
         <v>0.1877395256921193</v>
       </c>
-      <c r="AA37" t="n">
+      <c r="AC37" t="n">
         <v>0.1058797652858703</v>
       </c>
-      <c r="AB37" t="n">
+      <c r="AD37" t="n">
         <v>0.1105252100840336</v>
       </c>
-      <c r="AC37" t="n">
+      <c r="AE37" t="n">
         <v>0.08660600275610958</v>
       </c>
-      <c r="AD37" t="n">
+      <c r="AF37" t="n">
         <v>0.1002958579881657</v>
       </c>
-      <c r="AE37" t="n">
+      <c r="AG37" t="n">
         <v>0.03448275862068965</v>
       </c>
-      <c r="AF37" t="n">
+      <c r="AH37" t="n">
         <v>0.01342281879194631</v>
       </c>
-      <c r="AG37" t="n">
+      <c r="AI37" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4374,104 +4744,114 @@
       <c r="A38" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="B38" t="n">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>382.164</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>375.938</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
         <v>83.8</v>
       </c>
-      <c r="C38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" t="n">
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
         <v>16.2</v>
       </c>
-      <c r="E38" t="n">
+      <c r="G38" t="n">
         <v>27.32</v>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t xml:space="preserve">  I have to go to the ladies' room.  Do you want anything?  she inquired softly.  No, I'm fine.</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>milkywayoriginal_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H38" t="n">
+      <c r="J38" t="n">
         <v>0.1094838681045578</v>
       </c>
-      <c r="I38" t="n">
+      <c r="K38" t="n">
         <v>0.08035020965988507</v>
       </c>
-      <c r="J38" t="n">
+      <c r="L38" t="n">
         <v>0.06564885496183206</v>
       </c>
-      <c r="K38" t="n">
+      <c r="M38" t="n">
         <v>0.09962255390214861</v>
       </c>
-      <c r="L38" t="n">
+      <c r="N38" t="n">
         <v>0.09944841012329655</v>
       </c>
-      <c r="M38" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
       <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
         <v>0.02406417112299465</v>
       </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
         <v>0.5</v>
       </c>
-      <c r="S38" t="n">
+      <c r="U38" t="n">
         <v>0.07308970099667775</v>
       </c>
-      <c r="T38" t="n">
+      <c r="V38" t="n">
         <v>0.1844673501836724</v>
       </c>
-      <c r="U38" t="n">
+      <c r="W38" t="n">
         <v>0.09622641509433963</v>
       </c>
-      <c r="V38" t="n">
-        <v>0</v>
-      </c>
-      <c r="W38" t="n">
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
         <v>0.09464285714285714</v>
       </c>
-      <c r="X38" t="n">
+      <c r="Z38" t="n">
         <v>0.1913254537779654</v>
       </c>
-      <c r="Y38" t="n">
+      <c r="AA38" t="n">
         <v>0.07234042553191489</v>
       </c>
-      <c r="Z38" t="n">
+      <c r="AB38" t="n">
         <v>0.0958904109589041</v>
       </c>
-      <c r="AA38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB38" t="n">
+      <c r="AC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="n">
         <v>0.04411764705882353</v>
       </c>
-      <c r="AC38" t="n">
+      <c r="AE38" t="n">
         <v>0.1628605769230769</v>
       </c>
-      <c r="AD38" t="n">
+      <c r="AF38" t="n">
         <v>0.05</v>
       </c>
-      <c r="AE38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF38" t="n">
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
         <v>0.05128205128205128</v>
       </c>
-      <c r="AG38" t="n">
+      <c r="AI38" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -4479,104 +4859,114 @@
       <c r="A39" s="1" t="n">
         <v>37</v>
       </c>
-      <c r="B39" t="n">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>388.71</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>382.344</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
         <v>82.69999999999999</v>
       </c>
-      <c r="C39" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" t="n">
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="n">
         <v>17.3</v>
       </c>
-      <c r="E39" t="n">
+      <c r="G39" t="n">
         <v>58.59</v>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t xml:space="preserve">  I was just hoping to talk about our past, he answered.  By the way, do you have a Milky Way on you by any chance?</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>milkywayoriginal_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H39" t="n">
+      <c r="J39" t="n">
         <v>0.04374678332475553</v>
       </c>
-      <c r="I39" t="n">
+      <c r="K39" t="n">
         <v>0.04908020017243319</v>
       </c>
-      <c r="J39" t="n">
+      <c r="L39" t="n">
         <v>0.04958902769170553</v>
       </c>
-      <c r="K39" t="n">
+      <c r="M39" t="n">
         <v>0.04240965956678774</v>
       </c>
-      <c r="L39" t="n">
+      <c r="N39" t="n">
         <v>0.05226396917148363</v>
       </c>
-      <c r="M39" t="n">
+      <c r="O39" t="n">
         <v>0.06061329026298853</v>
       </c>
-      <c r="N39" t="n">
+      <c r="P39" t="n">
         <v>0.05227438775607026</v>
       </c>
-      <c r="O39" t="n">
+      <c r="Q39" t="n">
         <v>0.03953928624981257</v>
       </c>
-      <c r="P39" t="n">
+      <c r="R39" t="n">
         <v>0.03321970655512387</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="S39" t="n">
         <v>0.04677449255867695</v>
       </c>
-      <c r="R39" t="n">
+      <c r="T39" t="n">
         <v>3</v>
       </c>
-      <c r="S39" t="n">
+      <c r="U39" t="n">
         <v>0.118264221158958</v>
       </c>
-      <c r="T39" t="n">
+      <c r="V39" t="n">
         <v>0.1237965047188569</v>
       </c>
-      <c r="U39" t="n">
+      <c r="W39" t="n">
         <v>0.1627780628744896</v>
       </c>
-      <c r="V39" t="n">
+      <c r="X39" t="n">
         <v>0.06817910283551698</v>
       </c>
-      <c r="W39" t="n">
+      <c r="Y39" t="n">
         <v>0.1483572482742658</v>
       </c>
-      <c r="X39" t="n">
+      <c r="Z39" t="n">
         <v>0.1301584811977827</v>
       </c>
-      <c r="Y39" t="n">
+      <c r="AA39" t="n">
         <v>0.06000204960032793</v>
       </c>
-      <c r="Z39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA39" t="n">
+      <c r="AB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" t="n">
         <v>0.03866146848602989</v>
       </c>
-      <c r="AB39" t="n">
+      <c r="AD39" t="n">
         <v>0.01809523809523809</v>
       </c>
-      <c r="AC39" t="n">
+      <c r="AE39" t="n">
         <v>0.04242734044106908</v>
       </c>
-      <c r="AD39" t="n">
+      <c r="AF39" t="n">
         <v>0.01818181818181818</v>
       </c>
-      <c r="AE39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF39" t="n">
+      <c r="AG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="n">
         <v>0.04250927269795194</v>
       </c>
-      <c r="AG39" t="n">
+      <c r="AI39" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4584,104 +4974,114 @@
       <c r="A40" s="1" t="n">
         <v>38</v>
       </c>
-      <c r="B40" t="n">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>396.15</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>389.711</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
         <v>56.39999999999999</v>
       </c>
-      <c r="C40" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" t="n">
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
         <v>43.6</v>
       </c>
-      <c r="E40" t="n">
+      <c r="G40" t="n">
         <v>81.76000000000001</v>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t xml:space="preserve">  What?  No, she answered, looking at him tenderly.  Thomas felt like a confident man.</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>milkywayoriginal_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H40" t="n">
+      <c r="J40" t="n">
         <v>0.01784273768533483</v>
       </c>
-      <c r="I40" t="n">
+      <c r="K40" t="n">
         <v>0.05433647556561488</v>
       </c>
-      <c r="J40" t="n">
+      <c r="L40" t="n">
         <v>0.05185584775605005</v>
       </c>
-      <c r="K40" t="n">
+      <c r="M40" t="n">
         <v>0.009142776244071636</v>
       </c>
-      <c r="L40" t="n">
+      <c r="N40" t="n">
         <v>0.02465137201979307</v>
       </c>
-      <c r="M40" t="n">
+      <c r="O40" t="n">
         <v>0.06050116249031257</v>
       </c>
-      <c r="N40" t="n">
+      <c r="P40" t="n">
         <v>0.02575107296137339</v>
       </c>
-      <c r="O40" t="n">
+      <c r="Q40" t="n">
         <v>0.07315516785937276</v>
       </c>
-      <c r="P40" t="n">
+      <c r="R40" t="n">
         <v>0.06108078957058245</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="S40" t="n">
         <v>0.06614822376480196</v>
       </c>
-      <c r="R40" t="n">
+      <c r="T40" t="n">
         <v>1.666666666666667</v>
       </c>
-      <c r="S40" t="n">
+      <c r="U40" t="n">
         <v>0.09026275951557093</v>
       </c>
-      <c r="T40" t="n">
+      <c r="V40" t="n">
         <v>0.06236069641280121</v>
       </c>
-      <c r="U40" t="n">
+      <c r="W40" t="n">
         <v>0.05511039886039886</v>
       </c>
-      <c r="V40" t="n">
+      <c r="X40" t="n">
         <v>0.002471169686985173</v>
       </c>
-      <c r="W40" t="n">
+      <c r="Y40" t="n">
         <v>0.006809338521400778</v>
       </c>
-      <c r="X40" t="n">
+      <c r="Z40" t="n">
         <v>0.02799818291944276</v>
       </c>
-      <c r="Y40" t="n">
+      <c r="AA40" t="n">
         <v>0.03056053246270637</v>
       </c>
-      <c r="Z40" t="n">
+      <c r="AB40" t="n">
         <v>0.073001012145749</v>
       </c>
-      <c r="AA40" t="n">
+      <c r="AC40" t="n">
         <v>0.1043964277151762</v>
       </c>
-      <c r="AB40" t="n">
+      <c r="AD40" t="n">
         <v>0.04272151898734177</v>
       </c>
-      <c r="AC40" t="n">
+      <c r="AE40" t="n">
         <v>0.1261033324022873</v>
       </c>
-      <c r="AD40" t="n">
+      <c r="AF40" t="n">
         <v>0.1462335476262934</v>
       </c>
-      <c r="AE40" t="n">
+      <c r="AG40" t="n">
         <v>0.06666666666666667</v>
       </c>
-      <c r="AF40" t="n">
+      <c r="AH40" t="n">
         <v>0.0364963503649635</v>
       </c>
-      <c r="AG40" t="n">
+      <c r="AI40" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4689,104 +5089,114 @@
       <c r="A41" s="1" t="n">
         <v>39</v>
       </c>
-      <c r="B41" t="n">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>407.166</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>397.031</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
         <v>86.5</v>
       </c>
-      <c r="C41" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" t="n">
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
         <v>13.5</v>
       </c>
-      <c r="E41" t="n">
+      <c r="G41" t="n">
         <v>64.86</v>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t xml:space="preserve">  It's fine.  I'll be back in a jiffy, he said, as he leapt to find a vending machine.  On his way to his seat, while swallowing what was left of his chocolate, he smiled to himself.</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>milkywayoriginal_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H41" t="n">
+      <c r="J41" t="n">
         <v>0.01704545454545454</v>
       </c>
-      <c r="I41" t="n">
+      <c r="K41" t="n">
         <v>0.04069767441860465</v>
       </c>
-      <c r="J41" t="n">
+      <c r="L41" t="n">
         <v>0.01245232218981378</v>
       </c>
-      <c r="K41" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" t="n">
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
         <v>0.02403846153846154</v>
       </c>
-      <c r="M41" t="n">
+      <c r="O41" t="n">
         <v>0.07007818478261174</v>
       </c>
-      <c r="N41" t="n">
+      <c r="P41" t="n">
         <v>0.0727956396282106</v>
       </c>
-      <c r="O41" t="n">
+      <c r="Q41" t="n">
         <v>0.06699663561076603</v>
       </c>
-      <c r="P41" t="n">
+      <c r="R41" t="n">
         <v>0.06476672488917079</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="S41" t="n">
         <v>0.06076335646497797</v>
       </c>
-      <c r="R41" t="n">
+      <c r="T41" t="n">
         <v>0.5</v>
       </c>
-      <c r="S41" t="n">
+      <c r="U41" t="n">
         <v>0.03782894736842105</v>
       </c>
-      <c r="T41" t="n">
+      <c r="V41" t="n">
         <v>0.0897902336422034</v>
       </c>
-      <c r="U41" t="n">
+      <c r="W41" t="n">
         <v>0.0423728813559322</v>
       </c>
-      <c r="V41" t="n">
+      <c r="X41" t="n">
         <v>0.07175271158503083</v>
       </c>
-      <c r="W41" t="n">
+      <c r="Y41" t="n">
         <v>0.0548866144892635</v>
       </c>
-      <c r="X41" t="n">
+      <c r="Z41" t="n">
         <v>0.1189521675902999</v>
       </c>
-      <c r="Y41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z41" t="n">
+      <c r="AA41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB41" t="n">
         <v>0.08322841304143569</v>
       </c>
-      <c r="AA41" t="n">
+      <c r="AC41" t="n">
         <v>0.07509248844093645</v>
       </c>
-      <c r="AB41" t="n">
+      <c r="AD41" t="n">
         <v>0.100296862489109</v>
       </c>
-      <c r="AC41" t="n">
+      <c r="AE41" t="n">
         <v>0.0196554031448645</v>
       </c>
-      <c r="AD41" t="n">
+      <c r="AF41" t="n">
         <v>0.05641990165911215</v>
       </c>
-      <c r="AE41" t="n">
+      <c r="AG41" t="n">
         <v>0.01368876080691643</v>
       </c>
-      <c r="AF41" t="n">
+      <c r="AH41" t="n">
         <v>0.1149889433312176</v>
       </c>
-      <c r="AG41" t="n">
+      <c r="AI41" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -4794,104 +5204,114 @@
       <c r="A42" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="B42" t="n">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>416.495</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>407.947</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
         <v>85.90000000000001</v>
       </c>
-      <c r="C42" t="n">
+      <c r="E42" t="n">
         <v>5.5</v>
       </c>
-      <c r="D42" t="n">
+      <c r="F42" t="n">
         <v>8.6</v>
       </c>
-      <c r="E42" t="n">
+      <c r="G42" t="n">
         <v>22.83</v>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t xml:space="preserve">  Why didn't I go to that wacky hypnotist earlier?  I must never admit this to Mom.  He moved the chair with a big smile on his face.</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>milkywayoriginal_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H42" t="n">
+      <c r="J42" t="n">
         <v>0.03450059101654846</v>
       </c>
-      <c r="I42" t="n">
+      <c r="K42" t="n">
         <v>0.04803352675693102</v>
       </c>
-      <c r="J42" t="n">
+      <c r="L42" t="n">
         <v>0.06967414985317799</v>
       </c>
-      <c r="K42" t="n">
+      <c r="M42" t="n">
         <v>0.03001141552511415</v>
       </c>
-      <c r="L42" t="n">
+      <c r="N42" t="n">
         <v>0.03951997651184643</v>
       </c>
-      <c r="M42" t="n">
+      <c r="O42" t="n">
         <v>0.02994195688225539</v>
       </c>
-      <c r="N42" t="n">
+      <c r="P42" t="n">
         <v>0.05302537385870718</v>
       </c>
-      <c r="O42" t="n">
+      <c r="Q42" t="n">
         <v>0.02864449580551276</v>
       </c>
-      <c r="P42" t="n">
+      <c r="R42" t="n">
         <v>0.02690039437027389</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="S42" t="n">
         <v>0.04138764880952381</v>
       </c>
-      <c r="R42" t="n">
+      <c r="T42" t="n">
         <v>1.5</v>
       </c>
-      <c r="S42" t="n">
+      <c r="U42" t="n">
         <v>0.02027027027027027</v>
       </c>
-      <c r="T42" t="n">
+      <c r="V42" t="n">
         <v>0.09782017829963036</v>
       </c>
-      <c r="U42" t="n">
+      <c r="W42" t="n">
         <v>0.09795127353266889</v>
       </c>
-      <c r="V42" t="n">
+      <c r="X42" t="n">
         <v>0.08515151515151516</v>
       </c>
-      <c r="W42" t="n">
+      <c r="Y42" t="n">
         <v>0.1053317134378299</v>
       </c>
-      <c r="X42" t="n">
+      <c r="Z42" t="n">
         <v>0.007575757575757576</v>
       </c>
-      <c r="Y42" t="n">
+      <c r="AA42" t="n">
         <v>0.02564102564102564</v>
       </c>
-      <c r="Z42" t="n">
+      <c r="AB42" t="n">
         <v>0.1283536585365854</v>
       </c>
-      <c r="AA42" t="n">
+      <c r="AC42" t="n">
         <v>0.05607361963190184</v>
       </c>
-      <c r="AB42" t="n">
+      <c r="AD42" t="n">
         <v>0.04291044776119403</v>
       </c>
-      <c r="AC42" t="n">
+      <c r="AE42" t="n">
         <v>0.08366371268656717</v>
       </c>
-      <c r="AD42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE42" t="n">
+      <c r="AF42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="n">
         <v>0.06021409455842997</v>
       </c>
-      <c r="AF42" t="n">
+      <c r="AH42" t="n">
         <v>0.05500431406384815</v>
       </c>
-      <c r="AG42" t="n">
+      <c r="AI42" t="n">
         <v>0.6666666666666666</v>
       </c>
     </row>
